--- a/02-Execucao/03-Execucao_Procedimentos/02-Resultados_Auditoria/03-pos-comentarios-gestor/tabelas_consolidadas_auditoria.xlsx
+++ b/02-Execucao/03-Execucao_Procedimentos/02-Resultados_Auditoria/03-pos-comentarios-gestor/tabelas_consolidadas_auditoria.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6076" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6077" uniqueCount="311">
   <si>
     <t>Nome</t>
   </si>
@@ -5417,9 +5417,6 @@
       <c r="A72" t="s">
         <v>83</v>
       </c>
-      <c r="B72" t="s">
-        <v>256</v>
-      </c>
       <c r="C72" t="s">
         <v>256</v>
       </c>
@@ -6480,9 +6477,6 @@
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
-        <v>256</v>
-      </c>
       <c r="C3" t="s">
         <v>256</v>
       </c>
@@ -6737,9 +6731,6 @@
       <c r="D7" t="s">
         <v>256</v>
       </c>
-      <c r="H7" t="s">
-        <v>256</v>
-      </c>
       <c r="I7" t="s">
         <v>256</v>
       </c>
@@ -8615,9 +8606,6 @@
       <c r="Y37" t="s">
         <v>256</v>
       </c>
-      <c r="AA37" t="s">
-        <v>256</v>
-      </c>
     </row>
     <row r="38" spans="1:27">
       <c r="A38" t="s">
@@ -8812,6 +8800,9 @@
       <c r="L41" t="s">
         <v>256</v>
       </c>
+      <c r="M41" t="s">
+        <v>256</v>
+      </c>
       <c r="N41" t="s">
         <v>256</v>
       </c>
@@ -8862,6 +8853,9 @@
       <c r="H42" t="s">
         <v>256</v>
       </c>
+      <c r="M42" t="s">
+        <v>256</v>
+      </c>
       <c r="O42" t="s">
         <v>256</v>
       </c>
@@ -9560,6 +9554,9 @@
       <c r="I55" t="s">
         <v>256</v>
       </c>
+      <c r="M55" t="s">
+        <v>256</v>
+      </c>
       <c r="N55" t="s">
         <v>256</v>
       </c>
@@ -10192,9 +10189,6 @@
       <c r="M65" t="s">
         <v>256</v>
       </c>
-      <c r="N65" t="s">
-        <v>256</v>
-      </c>
       <c r="O65" t="s">
         <v>256</v>
       </c>
@@ -10545,9 +10539,6 @@
       <c r="D72" t="s">
         <v>256</v>
       </c>
-      <c r="G72" t="s">
-        <v>256</v>
-      </c>
       <c r="H72" t="s">
         <v>256</v>
       </c>
@@ -10770,6 +10761,9 @@
       <c r="Y75" t="s">
         <v>256</v>
       </c>
+      <c r="Z75" t="s">
+        <v>256</v>
+      </c>
       <c r="AA75" t="s">
         <v>256</v>
       </c>
@@ -10949,6 +10943,9 @@
       <c r="L79" t="s">
         <v>256</v>
       </c>
+      <c r="M79" t="s">
+        <v>256</v>
+      </c>
       <c r="N79" t="s">
         <v>256</v>
       </c>
@@ -12864,6 +12861,9 @@
         <v>256</v>
       </c>
       <c r="N109" t="s">
+        <v>256</v>
+      </c>
+      <c r="O109" t="s">
         <v>256</v>
       </c>
       <c r="Q109" t="s">
@@ -13390,9 +13390,6 @@
       <c r="E3" t="s">
         <v>256</v>
       </c>
-      <c r="G3" t="s">
-        <v>256</v>
-      </c>
       <c r="J3" t="s">
         <v>256</v>
       </c>
@@ -13668,9 +13665,6 @@
       <c r="O7" t="s">
         <v>256</v>
       </c>
-      <c r="P7" t="s">
-        <v>256</v>
-      </c>
       <c r="Q7" t="s">
         <v>256</v>
       </c>
@@ -15489,9 +15483,6 @@
       <c r="H37" t="s">
         <v>256</v>
       </c>
-      <c r="I37" t="s">
-        <v>256</v>
-      </c>
       <c r="L37" t="s">
         <v>256</v>
       </c>
@@ -15737,6 +15728,9 @@
       <c r="T41" t="s">
         <v>256</v>
       </c>
+      <c r="U41" t="s">
+        <v>256</v>
+      </c>
       <c r="V41" t="s">
         <v>256</v>
       </c>
@@ -15775,6 +15769,9 @@
       <c r="Q42" t="s">
         <v>256</v>
       </c>
+      <c r="U42" t="s">
+        <v>256</v>
+      </c>
       <c r="V42" t="s">
         <v>256</v>
       </c>
@@ -16488,6 +16485,9 @@
       <c r="T55" t="s">
         <v>256</v>
       </c>
+      <c r="U55" t="s">
+        <v>256</v>
+      </c>
       <c r="V55" t="s">
         <v>256</v>
       </c>
@@ -17075,9 +17075,6 @@
       <c r="C65" t="s">
         <v>256</v>
       </c>
-      <c r="E65" t="s">
-        <v>256</v>
-      </c>
       <c r="G65" t="s">
         <v>256</v>
       </c>
@@ -17443,9 +17440,6 @@
       <c r="A72" t="s">
         <v>83</v>
       </c>
-      <c r="C72" t="s">
-        <v>256</v>
-      </c>
       <c r="E72" t="s">
         <v>256</v>
       </c>
@@ -17650,6 +17644,9 @@
       <c r="I75" t="s">
         <v>256</v>
       </c>
+      <c r="J75" t="s">
+        <v>256</v>
+      </c>
       <c r="L75" t="s">
         <v>256</v>
       </c>
@@ -17880,6 +17877,9 @@
       <c r="T79" t="s">
         <v>256</v>
       </c>
+      <c r="U79" t="s">
+        <v>256</v>
+      </c>
       <c r="V79" t="s">
         <v>256</v>
       </c>
@@ -19771,6 +19771,9 @@
         <v>256</v>
       </c>
       <c r="L109" t="s">
+        <v>256</v>
+      </c>
+      <c r="N109" t="s">
         <v>256</v>
       </c>
       <c r="P109" t="s">
@@ -20684,7 +20687,7 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B49">
         <v>6</v>
@@ -20695,7 +20698,7 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B50">
         <v>6</v>
@@ -20706,7 +20709,7 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="B51">
         <v>6</v>
@@ -20717,7 +20720,7 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="B52">
         <v>6</v>
@@ -20728,7 +20731,7 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="B53">
         <v>6</v>
@@ -20739,29 +20742,29 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>110</v>
+        <v>34</v>
       </c>
       <c r="B54">
         <v>6</v>
       </c>
       <c r="C54">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="B55">
         <v>6</v>
       </c>
       <c r="C55">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="B56">
         <v>6</v>
@@ -20772,18 +20775,18 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="B57">
         <v>6</v>
       </c>
       <c r="C57">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B58">
         <v>6</v>
@@ -20794,29 +20797,29 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B59">
         <v>6</v>
       </c>
       <c r="C59">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="B60">
         <v>6</v>
       </c>
       <c r="C60">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="B61">
         <v>6</v>
@@ -20827,7 +20830,7 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="B62">
         <v>6</v>
@@ -20838,7 +20841,7 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="B63">
         <v>6</v>
@@ -20849,7 +20852,7 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>62</v>
+        <v>115</v>
       </c>
       <c r="B64">
         <v>6</v>
@@ -20860,40 +20863,40 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>115</v>
+        <v>38</v>
       </c>
       <c r="B65">
         <v>6</v>
       </c>
       <c r="C65">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>38</v>
+        <v>101</v>
       </c>
       <c r="B66">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C66">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="B67">
         <v>5</v>
       </c>
       <c r="C67">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="B68">
         <v>5</v>
@@ -20904,7 +20907,7 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B69">
         <v>5</v>
@@ -20915,7 +20918,7 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="B70">
         <v>5</v>
@@ -20926,18 +20929,18 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>111</v>
+        <v>22</v>
       </c>
       <c r="B71">
         <v>5</v>
       </c>
       <c r="C71">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B72">
         <v>5</v>
@@ -20948,7 +20951,7 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="B73">
         <v>5</v>
@@ -20959,7 +20962,7 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="B74">
         <v>5</v>
@@ -20970,7 +20973,7 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="B75">
         <v>5</v>
@@ -20981,13 +20984,13 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>121</v>
+        <v>12</v>
       </c>
       <c r="B76">
         <v>5</v>
       </c>
       <c r="C76">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -21025,7 +21028,7 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="B80">
         <v>5</v>
@@ -21036,7 +21039,7 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B81">
         <v>5</v>
@@ -21047,7 +21050,7 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="B82">
         <v>5</v>
@@ -21113,18 +21116,18 @@
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="B88">
         <v>5</v>
       </c>
       <c r="C88">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="B89">
         <v>5</v>
@@ -21135,7 +21138,7 @@
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B90">
         <v>5</v>
@@ -21146,7 +21149,7 @@
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B91">
         <v>5</v>
@@ -21157,7 +21160,7 @@
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B92">
         <v>5</v>
@@ -21168,7 +21171,7 @@
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="B93">
         <v>5</v>
@@ -21262,12 +21265,12 @@
         <v>5</v>
       </c>
       <c r="C101">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>108</v>
+        <v>64</v>
       </c>
       <c r="B102">
         <v>5</v>
@@ -21278,7 +21281,7 @@
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="B103">
         <v>5</v>
@@ -21289,18 +21292,18 @@
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>42</v>
+        <v>117</v>
       </c>
       <c r="B104">
         <v>5</v>
       </c>
       <c r="C104">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="B105">
         <v>5</v>
@@ -21317,7 +21320,7 @@
         <v>5</v>
       </c>
       <c r="C106">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -21405,7 +21408,7 @@
         <v>2</v>
       </c>
       <c r="C114">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/02-Execucao/03-Execucao_Procedimentos/02-Resultados_Auditoria/03-pos-comentarios-gestor/tabelas_consolidadas_auditoria.xlsx
+++ b/02-Execucao/03-Execucao_Procedimentos/02-Resultados_Auditoria/03-pos-comentarios-gestor/tabelas_consolidadas_auditoria.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6077" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6103" uniqueCount="311">
   <si>
     <t>Nome</t>
   </si>
@@ -5417,6 +5417,9 @@
       <c r="A72" t="s">
         <v>83</v>
       </c>
+      <c r="B72" t="s">
+        <v>256</v>
+      </c>
       <c r="C72" t="s">
         <v>256</v>
       </c>
@@ -6201,6 +6204,9 @@
     <row r="109" spans="1:7">
       <c r="A109" t="s">
         <v>120</v>
+      </c>
+      <c r="B109" t="s">
+        <v>256</v>
       </c>
       <c r="C109" t="s">
         <v>256</v>
@@ -6486,9 +6492,6 @@
       <c r="H3" t="s">
         <v>256</v>
       </c>
-      <c r="M3" t="s">
-        <v>256</v>
-      </c>
       <c r="N3" t="s">
         <v>256</v>
       </c>
@@ -6502,6 +6505,12 @@
         <v>256</v>
       </c>
       <c r="S3" t="s">
+        <v>256</v>
+      </c>
+      <c r="W3" t="s">
+        <v>256</v>
+      </c>
+      <c r="X3" t="s">
         <v>256</v>
       </c>
       <c r="Y3" t="s">
@@ -6731,6 +6740,9 @@
       <c r="D7" t="s">
         <v>256</v>
       </c>
+      <c r="H7" t="s">
+        <v>256</v>
+      </c>
       <c r="I7" t="s">
         <v>256</v>
       </c>
@@ -6759,9 +6771,6 @@
         <v>256</v>
       </c>
       <c r="T7" t="s">
-        <v>256</v>
-      </c>
-      <c r="U7" t="s">
         <v>256</v>
       </c>
       <c r="V7" t="s">
@@ -8166,9 +8175,6 @@
       <c r="L30" t="s">
         <v>256</v>
       </c>
-      <c r="M30" t="s">
-        <v>256</v>
-      </c>
       <c r="N30" t="s">
         <v>256</v>
       </c>
@@ -8464,9 +8470,6 @@
       <c r="K35" t="s">
         <v>256</v>
       </c>
-      <c r="M35" t="s">
-        <v>256</v>
-      </c>
       <c r="N35" t="s">
         <v>256</v>
       </c>
@@ -8517,9 +8520,6 @@
       <c r="K36" t="s">
         <v>256</v>
       </c>
-      <c r="M36" t="s">
-        <v>256</v>
-      </c>
       <c r="N36" t="s">
         <v>256</v>
       </c>
@@ -8603,7 +8603,16 @@
       <c r="V37" t="s">
         <v>256</v>
       </c>
+      <c r="W37" t="s">
+        <v>256</v>
+      </c>
+      <c r="X37" t="s">
+        <v>256</v>
+      </c>
       <c r="Y37" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA37" t="s">
         <v>256</v>
       </c>
     </row>
@@ -8614,6 +8623,9 @@
       <c r="C38" t="s">
         <v>256</v>
       </c>
+      <c r="D38" t="s">
+        <v>256</v>
+      </c>
       <c r="E38" t="s">
         <v>256</v>
       </c>
@@ -8800,9 +8812,6 @@
       <c r="L41" t="s">
         <v>256</v>
       </c>
-      <c r="M41" t="s">
-        <v>256</v>
-      </c>
       <c r="N41" t="s">
         <v>256</v>
       </c>
@@ -9047,6 +9056,9 @@
       <c r="Y46" t="s">
         <v>256</v>
       </c>
+      <c r="AA46" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="47" spans="1:27">
       <c r="A47" t="s">
@@ -9554,9 +9566,6 @@
       <c r="I55" t="s">
         <v>256</v>
       </c>
-      <c r="M55" t="s">
-        <v>256</v>
-      </c>
       <c r="N55" t="s">
         <v>256</v>
       </c>
@@ -10186,7 +10195,7 @@
       <c r="K65" t="s">
         <v>256</v>
       </c>
-      <c r="M65" t="s">
+      <c r="N65" t="s">
         <v>256</v>
       </c>
       <c r="O65" t="s">
@@ -10250,6 +10259,9 @@
       <c r="A67" t="s">
         <v>76</v>
       </c>
+      <c r="B67" t="s">
+        <v>256</v>
+      </c>
       <c r="D67" t="s">
         <v>256</v>
       </c>
@@ -10284,9 +10296,6 @@
         <v>256</v>
       </c>
       <c r="T67" t="s">
-        <v>256</v>
-      </c>
-      <c r="U67" t="s">
         <v>256</v>
       </c>
       <c r="V67" t="s">
@@ -10401,6 +10410,9 @@
       <c r="O69" t="s">
         <v>256</v>
       </c>
+      <c r="R69" t="s">
+        <v>256</v>
+      </c>
       <c r="S69" t="s">
         <v>256</v>
       </c>
@@ -10539,6 +10551,9 @@
       <c r="D72" t="s">
         <v>256</v>
       </c>
+      <c r="G72" t="s">
+        <v>256</v>
+      </c>
       <c r="H72" t="s">
         <v>256</v>
       </c>
@@ -10576,6 +10591,12 @@
         <v>256</v>
       </c>
       <c r="V72" t="s">
+        <v>256</v>
+      </c>
+      <c r="W72" t="s">
+        <v>256</v>
+      </c>
+      <c r="X72" t="s">
         <v>256</v>
       </c>
       <c r="Y72" t="s">
@@ -10737,9 +10758,6 @@
       <c r="L75" t="s">
         <v>256</v>
       </c>
-      <c r="M75" t="s">
-        <v>256</v>
-      </c>
       <c r="N75" t="s">
         <v>256</v>
       </c>
@@ -10756,6 +10774,12 @@
         <v>256</v>
       </c>
       <c r="V75" t="s">
+        <v>256</v>
+      </c>
+      <c r="W75" t="s">
+        <v>256</v>
+      </c>
+      <c r="X75" t="s">
         <v>256</v>
       </c>
       <c r="Y75" t="s">
@@ -11197,6 +11221,9 @@
       <c r="C83" t="s">
         <v>256</v>
       </c>
+      <c r="D83" t="s">
+        <v>256</v>
+      </c>
       <c r="H83" t="s">
         <v>256</v>
       </c>
@@ -11321,9 +11348,6 @@
       <c r="A85" t="s">
         <v>96</v>
       </c>
-      <c r="D85" t="s">
-        <v>256</v>
-      </c>
       <c r="H85" t="s">
         <v>256</v>
       </c>
@@ -11534,9 +11558,6 @@
       <c r="R88" t="s">
         <v>256</v>
       </c>
-      <c r="S88" t="s">
-        <v>256</v>
-      </c>
       <c r="T88" t="s">
         <v>256</v>
       </c>
@@ -12577,6 +12598,9 @@
       <c r="S104" t="s">
         <v>256</v>
       </c>
+      <c r="T104" t="s">
+        <v>256</v>
+      </c>
       <c r="V104" t="s">
         <v>256</v>
       </c>
@@ -12665,6 +12689,9 @@
       <c r="I106" t="s">
         <v>256</v>
       </c>
+      <c r="L106" t="s">
+        <v>256</v>
+      </c>
       <c r="M106" t="s">
         <v>256</v>
       </c>
@@ -12686,6 +12713,9 @@
       <c r="T106" t="s">
         <v>256</v>
       </c>
+      <c r="V106" t="s">
+        <v>256</v>
+      </c>
       <c r="W106" t="s">
         <v>256</v>
       </c>
@@ -12693,6 +12723,9 @@
         <v>256</v>
       </c>
       <c r="Y106" t="s">
+        <v>256</v>
+      </c>
+      <c r="Z106" t="s">
         <v>256</v>
       </c>
       <c r="AA106" t="s">
@@ -12841,6 +12874,15 @@
     <row r="109" spans="1:27">
       <c r="A109" t="s">
         <v>120</v>
+      </c>
+      <c r="C109" t="s">
+        <v>256</v>
+      </c>
+      <c r="D109" t="s">
+        <v>256</v>
+      </c>
+      <c r="G109" t="s">
+        <v>256</v>
       </c>
       <c r="H109" t="s">
         <v>256</v>
@@ -13393,6 +13435,9 @@
       <c r="J3" t="s">
         <v>256</v>
       </c>
+      <c r="K3" t="s">
+        <v>256</v>
+      </c>
       <c r="M3" t="s">
         <v>256</v>
       </c>
@@ -13408,9 +13453,6 @@
       <c r="Q3" t="s">
         <v>256</v>
       </c>
-      <c r="U3" t="s">
-        <v>256</v>
-      </c>
       <c r="V3" t="s">
         <v>256</v>
       </c>
@@ -13418,6 +13460,9 @@
         <v>256</v>
       </c>
       <c r="X3" t="s">
+        <v>256</v>
+      </c>
+      <c r="Z3" t="s">
         <v>256</v>
       </c>
     </row>
@@ -13638,9 +13683,6 @@
       <c r="E7" t="s">
         <v>256</v>
       </c>
-      <c r="F7" t="s">
-        <v>256</v>
-      </c>
       <c r="G7" t="s">
         <v>256</v>
       </c>
@@ -13663,6 +13705,9 @@
         <v>256</v>
       </c>
       <c r="O7" t="s">
+        <v>256</v>
+      </c>
+      <c r="P7" t="s">
         <v>256</v>
       </c>
       <c r="Q7" t="s">
@@ -15094,9 +15139,6 @@
       <c r="T30" t="s">
         <v>256</v>
       </c>
-      <c r="U30" t="s">
-        <v>256</v>
-      </c>
       <c r="V30" t="s">
         <v>256</v>
       </c>
@@ -15383,9 +15425,6 @@
       <c r="T35" t="s">
         <v>256</v>
       </c>
-      <c r="U35" t="s">
-        <v>256</v>
-      </c>
       <c r="V35" t="s">
         <v>256</v>
       </c>
@@ -15445,9 +15484,6 @@
       <c r="T36" t="s">
         <v>256</v>
       </c>
-      <c r="U36" t="s">
-        <v>256</v>
-      </c>
       <c r="V36" t="s">
         <v>256</v>
       </c>
@@ -15483,6 +15519,12 @@
       <c r="H37" t="s">
         <v>256</v>
       </c>
+      <c r="I37" t="s">
+        <v>256</v>
+      </c>
+      <c r="K37" t="s">
+        <v>256</v>
+      </c>
       <c r="L37" t="s">
         <v>256</v>
       </c>
@@ -15511,6 +15553,9 @@
         <v>256</v>
       </c>
       <c r="Y37" t="s">
+        <v>256</v>
+      </c>
+      <c r="Z37" t="s">
         <v>256</v>
       </c>
       <c r="AA37" t="s">
@@ -15551,6 +15596,9 @@
       <c r="N38" t="s">
         <v>256</v>
       </c>
+      <c r="O38" t="s">
+        <v>256</v>
+      </c>
       <c r="P38" t="s">
         <v>256</v>
       </c>
@@ -15728,9 +15776,6 @@
       <c r="T41" t="s">
         <v>256</v>
       </c>
-      <c r="U41" t="s">
-        <v>256</v>
-      </c>
       <c r="V41" t="s">
         <v>256</v>
       </c>
@@ -15918,6 +15963,9 @@
       <c r="F46" t="s">
         <v>256</v>
       </c>
+      <c r="I46" t="s">
+        <v>256</v>
+      </c>
       <c r="K46" t="s">
         <v>256</v>
       </c>
@@ -16485,9 +16533,6 @@
       <c r="T55" t="s">
         <v>256</v>
       </c>
-      <c r="U55" t="s">
-        <v>256</v>
-      </c>
       <c r="V55" t="s">
         <v>256</v>
       </c>
@@ -17075,6 +17120,9 @@
       <c r="C65" t="s">
         <v>256</v>
       </c>
+      <c r="E65" t="s">
+        <v>256</v>
+      </c>
       <c r="G65" t="s">
         <v>256</v>
       </c>
@@ -17103,9 +17151,6 @@
         <v>256</v>
       </c>
       <c r="T65" t="s">
-        <v>256</v>
-      </c>
-      <c r="U65" t="s">
         <v>256</v>
       </c>
       <c r="V65" t="s">
@@ -17166,7 +17211,7 @@
       <c r="E67" t="s">
         <v>256</v>
       </c>
-      <c r="F67" t="s">
+      <c r="G67" t="s">
         <v>256</v>
       </c>
       <c r="H67" t="s">
@@ -17326,6 +17371,9 @@
       <c r="U69" t="s">
         <v>256</v>
       </c>
+      <c r="W69" t="s">
+        <v>256</v>
+      </c>
       <c r="X69" t="s">
         <v>256</v>
       </c>
@@ -17440,6 +17488,9 @@
       <c r="A72" t="s">
         <v>83</v>
       </c>
+      <c r="C72" t="s">
+        <v>256</v>
+      </c>
       <c r="E72" t="s">
         <v>256</v>
       </c>
@@ -17455,6 +17506,9 @@
       <c r="J72" t="s">
         <v>256</v>
       </c>
+      <c r="K72" t="s">
+        <v>256</v>
+      </c>
       <c r="L72" t="s">
         <v>256</v>
       </c>
@@ -17492,6 +17546,9 @@
         <v>256</v>
       </c>
       <c r="Y72" t="s">
+        <v>256</v>
+      </c>
+      <c r="Z72" t="s">
         <v>256</v>
       </c>
     </row>
@@ -17647,6 +17704,9 @@
       <c r="J75" t="s">
         <v>256</v>
       </c>
+      <c r="K75" t="s">
+        <v>256</v>
+      </c>
       <c r="L75" t="s">
         <v>256</v>
       </c>
@@ -17665,13 +17725,13 @@
       <c r="T75" t="s">
         <v>256</v>
       </c>
-      <c r="U75" t="s">
-        <v>256</v>
-      </c>
       <c r="V75" t="s">
         <v>256</v>
       </c>
       <c r="W75" t="s">
+        <v>256</v>
+      </c>
+      <c r="Z75" t="s">
         <v>256</v>
       </c>
       <c r="AA75" t="s">
@@ -18128,6 +18188,9 @@
       <c r="N83" t="s">
         <v>256</v>
       </c>
+      <c r="O83" t="s">
+        <v>256</v>
+      </c>
       <c r="P83" t="s">
         <v>256</v>
       </c>
@@ -18255,9 +18318,6 @@
       <c r="N85" t="s">
         <v>256</v>
       </c>
-      <c r="O85" t="s">
-        <v>256</v>
-      </c>
       <c r="P85" t="s">
         <v>256</v>
       </c>
@@ -18465,9 +18525,6 @@
       <c r="W88" t="s">
         <v>256</v>
       </c>
-      <c r="X88" t="s">
-        <v>256</v>
-      </c>
       <c r="Z88" t="s">
         <v>256</v>
       </c>
@@ -19478,6 +19535,9 @@
       <c r="Q104" t="s">
         <v>256</v>
       </c>
+      <c r="S104" t="s">
+        <v>256</v>
+      </c>
       <c r="T104" t="s">
         <v>256</v>
       </c>
@@ -19569,10 +19629,19 @@
       <c r="E106" t="s">
         <v>256</v>
       </c>
+      <c r="H106" t="s">
+        <v>256</v>
+      </c>
       <c r="I106" t="s">
         <v>256</v>
       </c>
+      <c r="J106" t="s">
+        <v>256</v>
+      </c>
       <c r="K106" t="s">
+        <v>256</v>
+      </c>
+      <c r="L106" t="s">
         <v>256</v>
       </c>
       <c r="N106" t="s">
@@ -19752,6 +19821,9 @@
       <c r="A109" t="s">
         <v>120</v>
       </c>
+      <c r="C109" t="s">
+        <v>256</v>
+      </c>
       <c r="E109" t="s">
         <v>256</v>
       </c>
@@ -19773,7 +19845,13 @@
       <c r="L109" t="s">
         <v>256</v>
       </c>
+      <c r="M109" t="s">
+        <v>256</v>
+      </c>
       <c r="N109" t="s">
+        <v>256</v>
+      </c>
+      <c r="O109" t="s">
         <v>256</v>
       </c>
       <c r="P109" t="s">
@@ -20379,7 +20457,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B21">
         <v>6</v>
@@ -20390,18 +20468,18 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="B22">
         <v>6</v>
       </c>
       <c r="C22">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B23">
         <v>6</v>
@@ -20412,7 +20490,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B24">
         <v>6</v>
@@ -20423,7 +20501,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>92</v>
+        <v>35</v>
       </c>
       <c r="B25">
         <v>6</v>
@@ -20434,7 +20512,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="B26">
         <v>6</v>
@@ -20445,7 +20523,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="B27">
         <v>6</v>
@@ -20456,7 +20534,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="B28">
         <v>6</v>
@@ -20467,7 +20545,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="B29">
         <v>6</v>
@@ -20478,7 +20556,7 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="B30">
         <v>6</v>
@@ -20489,40 +20567,40 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>9</v>
+        <v>105</v>
       </c>
       <c r="B31">
         <v>6</v>
       </c>
       <c r="C31">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>118</v>
       </c>
       <c r="B32">
         <v>6</v>
       </c>
       <c r="C32">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>21</v>
+        <v>125</v>
       </c>
       <c r="B33">
         <v>6</v>
       </c>
       <c r="C33">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B34">
         <v>6</v>
@@ -20533,7 +20611,7 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="B35">
         <v>6</v>
@@ -20544,7 +20622,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="B36">
         <v>6</v>
@@ -20555,7 +20633,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="B37">
         <v>6</v>
@@ -20566,7 +20644,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="B38">
         <v>6</v>
@@ -20577,7 +20655,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="B39">
         <v>6</v>
@@ -20588,7 +20666,7 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B40">
         <v>6</v>
@@ -20599,7 +20677,7 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B41">
         <v>6</v>
@@ -20610,7 +20688,7 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B42">
         <v>6</v>
@@ -20621,7 +20699,7 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B43">
         <v>6</v>
@@ -20632,7 +20710,7 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B44">
         <v>6</v>
@@ -20643,7 +20721,7 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="B45">
         <v>6</v>
@@ -20654,7 +20732,7 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="B46">
         <v>6</v>
@@ -20665,29 +20743,29 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="B47">
         <v>6</v>
       </c>
       <c r="C47">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
       <c r="B48">
         <v>6</v>
       </c>
       <c r="C48">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="B49">
         <v>6</v>
@@ -20698,7 +20776,7 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="B50">
         <v>6</v>
@@ -20709,7 +20787,7 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="B51">
         <v>6</v>
@@ -20720,7 +20798,7 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="B52">
         <v>6</v>
@@ -20731,7 +20809,7 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="B53">
         <v>6</v>
@@ -20742,29 +20820,29 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="B54">
         <v>6</v>
       </c>
       <c r="C54">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="B55">
         <v>6</v>
       </c>
       <c r="C55">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="B56">
         <v>6</v>
@@ -20775,73 +20853,73 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="B57">
         <v>6</v>
       </c>
       <c r="C57">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="B58">
         <v>6</v>
       </c>
       <c r="C58">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="B59">
         <v>6</v>
       </c>
       <c r="C59">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B60">
         <v>6</v>
       </c>
       <c r="C60">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B61">
         <v>6</v>
       </c>
       <c r="C61">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="B62">
         <v>6</v>
       </c>
       <c r="C62">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="B63">
         <v>6</v>
@@ -20852,7 +20930,7 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>115</v>
+        <v>16</v>
       </c>
       <c r="B64">
         <v>6</v>
@@ -20863,51 +20941,51 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="B65">
         <v>6</v>
       </c>
       <c r="C65">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="B66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C66">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="B67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C67">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="B68">
         <v>5</v>
       </c>
       <c r="C68">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>95</v>
+        <v>24</v>
       </c>
       <c r="B69">
         <v>5</v>
@@ -20918,7 +20996,7 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="B70">
         <v>5</v>
@@ -20929,29 +21007,29 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>22</v>
+        <v>95</v>
       </c>
       <c r="B71">
         <v>5</v>
       </c>
       <c r="C71">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>43</v>
+        <v>111</v>
       </c>
       <c r="B72">
         <v>5</v>
       </c>
       <c r="C72">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="B73">
         <v>5</v>
@@ -21028,7 +21106,7 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="B80">
         <v>5</v>
@@ -21039,7 +21117,7 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="B81">
         <v>5</v>
@@ -21050,7 +21128,7 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="B82">
         <v>5</v>
@@ -21061,7 +21139,7 @@
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="B83">
         <v>5</v>
@@ -21072,7 +21150,7 @@
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B84">
         <v>5</v>
@@ -21083,7 +21161,7 @@
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B85">
         <v>5</v>
@@ -21094,7 +21172,7 @@
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B86">
         <v>5</v>
@@ -21105,7 +21183,7 @@
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="B87">
         <v>5</v>
@@ -21116,7 +21194,7 @@
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B88">
         <v>5</v>
@@ -21138,7 +21216,7 @@
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B90">
         <v>5</v>
@@ -21149,7 +21227,7 @@
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B91">
         <v>5</v>
@@ -21160,7 +21238,7 @@
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B92">
         <v>5</v>
@@ -21171,7 +21249,7 @@
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B93">
         <v>5</v>
@@ -21182,18 +21260,18 @@
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>20</v>
+        <v>106</v>
       </c>
       <c r="B94">
         <v>5</v>
       </c>
       <c r="C94">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="B95">
         <v>5</v>
@@ -21204,18 +21282,18 @@
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>37</v>
+        <v>117</v>
       </c>
       <c r="B96">
         <v>5</v>
       </c>
       <c r="C96">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B97">
         <v>5</v>
@@ -21226,7 +21304,7 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B98">
         <v>5</v>
@@ -21237,7 +21315,7 @@
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="B99">
         <v>5</v>
@@ -21248,35 +21326,35 @@
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="B100">
         <v>5</v>
       </c>
       <c r="C100">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="B101">
         <v>5</v>
       </c>
       <c r="C101">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="B102">
         <v>5</v>
       </c>
       <c r="C102">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -21292,35 +21370,35 @@
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="B104">
         <v>5</v>
       </c>
       <c r="C104">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="B105">
         <v>5</v>
       </c>
       <c r="C105">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="B106">
         <v>5</v>
       </c>
       <c r="C106">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="107" spans="1:3">

--- a/02-Execucao/03-Execucao_Procedimentos/02-Resultados_Auditoria/03-pos-comentarios-gestor/tabelas_consolidadas_auditoria.xlsx
+++ b/02-Execucao/03-Execucao_Procedimentos/02-Resultados_Auditoria/03-pos-comentarios-gestor/tabelas_consolidadas_auditoria.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4718" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4774" uniqueCount="310">
   <si>
     <t>Nome</t>
   </si>
@@ -796,6 +796,9 @@
   </si>
   <si>
     <t>[Determinação] assegure que as contratações de TIC sejam compatíveis com os instrumentos de planejamento de TIC e, quando elaborado, com o Plano de Contratações Anual, promovendo os ajustes ou justificativas cabíveis nos casos excepcionais</t>
+  </si>
+  <si>
+    <t>[Determinação] defina formalmente as atribuições da área de TIC, atentando-se, minimamente, em abranger as atividades de planejamento, coordenação, gestão e controle da TIC</t>
   </si>
   <si>
     <t>[Determinação] estabeleça e execute rotina periódica de acompanhamento da execução do plano de TIC, promovendo sua revisão periódica e os ajustes ou atualizações necessários, com registro das principais decisões e reprogramações</t>
@@ -6250,10 +6253,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z114"/>
+  <dimension ref="A1:AA114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -6332,59 +6335,62 @@
       <c r="Z1" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="2" spans="1:26">
+      <c r="AA1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27">
       <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="L2" t="s">
-        <v>256</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="D2" t="s">
+        <v>256</v>
+      </c>
+      <c r="M2" t="s">
         <v>256</v>
       </c>
       <c r="P2" t="s">
         <v>256</v>
       </c>
-      <c r="R2" t="s">
-        <v>256</v>
-      </c>
-      <c r="T2" t="s">
+      <c r="Q2" t="s">
+        <v>256</v>
+      </c>
+      <c r="S2" t="s">
         <v>256</v>
       </c>
       <c r="U2" t="s">
         <v>256</v>
       </c>
-      <c r="W2" t="s">
+      <c r="V2" t="s">
         <v>256</v>
       </c>
       <c r="X2" t="s">
         <v>256</v>
       </c>
-      <c r="Z2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26">
+      <c r="Y2" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27">
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="H3" t="s">
-        <v>256</v>
-      </c>
       <c r="I3" t="s">
         <v>256</v>
       </c>
-      <c r="L3" t="s">
-        <v>256</v>
-      </c>
-      <c r="T3" t="s">
+      <c r="J3" t="s">
+        <v>256</v>
+      </c>
+      <c r="M3" t="s">
         <v>256</v>
       </c>
       <c r="U3" t="s">
         <v>256</v>
       </c>
-      <c r="W3" t="s">
+      <c r="V3" t="s">
         <v>256</v>
       </c>
       <c r="X3" t="s">
@@ -6393,27 +6399,30 @@
       <c r="Y3" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="4" spans="1:26">
+      <c r="Z3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27">
       <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="E4" t="s">
+      <c r="D4" t="s">
         <v>256</v>
       </c>
       <c r="F4" t="s">
         <v>256</v>
       </c>
-      <c r="L4" t="s">
-        <v>256</v>
-      </c>
-      <c r="O4" t="s">
+      <c r="G4" t="s">
+        <v>256</v>
+      </c>
+      <c r="M4" t="s">
         <v>256</v>
       </c>
       <c r="P4" t="s">
         <v>256</v>
       </c>
-      <c r="R4" t="s">
+      <c r="Q4" t="s">
         <v>256</v>
       </c>
       <c r="S4" t="s">
@@ -6425,7 +6434,7 @@
       <c r="U4" t="s">
         <v>256</v>
       </c>
-      <c r="W4" t="s">
+      <c r="V4" t="s">
         <v>256</v>
       </c>
       <c r="X4" t="s">
@@ -6437,24 +6446,27 @@
       <c r="Z4" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="5" spans="1:26">
+      <c r="AA4" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27">
       <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="C5" t="s">
         <v>256</v>
       </c>
-      <c r="E5" t="s">
+      <c r="D5" t="s">
         <v>256</v>
       </c>
       <c r="F5" t="s">
         <v>256</v>
       </c>
-      <c r="L5" t="s">
-        <v>256</v>
-      </c>
-      <c r="O5" t="s">
+      <c r="G5" t="s">
+        <v>256</v>
+      </c>
+      <c r="M5" t="s">
         <v>256</v>
       </c>
       <c r="P5" t="s">
@@ -6475,7 +6487,7 @@
       <c r="U5" t="s">
         <v>256</v>
       </c>
-      <c r="W5" t="s">
+      <c r="V5" t="s">
         <v>256</v>
       </c>
       <c r="X5" t="s">
@@ -6487,24 +6499,27 @@
       <c r="Z5" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="6" spans="1:26">
+      <c r="AA5" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27">
       <c r="A6" t="s">
         <v>11</v>
       </c>
       <c r="C6" t="s">
         <v>256</v>
       </c>
-      <c r="E6" t="s">
+      <c r="D6" t="s">
         <v>256</v>
       </c>
       <c r="F6" t="s">
         <v>256</v>
       </c>
-      <c r="L6" t="s">
-        <v>256</v>
-      </c>
-      <c r="O6" t="s">
+      <c r="G6" t="s">
+        <v>256</v>
+      </c>
+      <c r="M6" t="s">
         <v>256</v>
       </c>
       <c r="P6" t="s">
@@ -6525,7 +6540,7 @@
       <c r="U6" t="s">
         <v>256</v>
       </c>
-      <c r="W6" t="s">
+      <c r="V6" t="s">
         <v>256</v>
       </c>
       <c r="X6" t="s">
@@ -6537,24 +6552,24 @@
       <c r="Z6" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="7" spans="1:26">
+      <c r="AA6" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27">
       <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>256</v>
       </c>
-      <c r="F7" t="s">
-        <v>256</v>
-      </c>
-      <c r="L7" t="s">
-        <v>256</v>
-      </c>
-      <c r="P7" t="s">
-        <v>256</v>
-      </c>
-      <c r="R7" t="s">
+      <c r="G7" t="s">
+        <v>256</v>
+      </c>
+      <c r="M7" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q7" t="s">
         <v>256</v>
       </c>
       <c r="S7" t="s">
@@ -6566,7 +6581,7 @@
       <c r="U7" t="s">
         <v>256</v>
       </c>
-      <c r="W7" t="s">
+      <c r="V7" t="s">
         <v>256</v>
       </c>
       <c r="X7" t="s">
@@ -6578,33 +6593,33 @@
       <c r="Z7" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="8" spans="1:26">
+      <c r="AA7" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27">
       <c r="A8" t="s">
         <v>13</v>
       </c>
       <c r="C8" t="s">
         <v>256</v>
       </c>
-      <c r="E8" t="s">
-        <v>256</v>
-      </c>
       <c r="F8" t="s">
         <v>256</v>
       </c>
-      <c r="N8" t="s">
-        <v>256</v>
-      </c>
-      <c r="P8" t="s">
+      <c r="G8" t="s">
+        <v>256</v>
+      </c>
+      <c r="O8" t="s">
         <v>256</v>
       </c>
       <c r="Q8" t="s">
         <v>256</v>
       </c>
-      <c r="U8" t="s">
-        <v>256</v>
-      </c>
-      <c r="W8" t="s">
+      <c r="R8" t="s">
+        <v>256</v>
+      </c>
+      <c r="V8" t="s">
         <v>256</v>
       </c>
       <c r="X8" t="s">
@@ -6616,18 +6631,21 @@
       <c r="Z8" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="9" spans="1:26">
+      <c r="AA8" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27">
       <c r="A9" t="s">
         <v>15</v>
       </c>
-      <c r="E9" t="s">
+      <c r="D9" t="s">
         <v>256</v>
       </c>
       <c r="F9" t="s">
         <v>256</v>
       </c>
-      <c r="N9" t="s">
+      <c r="G9" t="s">
         <v>256</v>
       </c>
       <c r="O9" t="s">
@@ -6651,7 +6669,7 @@
       <c r="U9" t="s">
         <v>256</v>
       </c>
-      <c r="W9" t="s">
+      <c r="V9" t="s">
         <v>256</v>
       </c>
       <c r="X9" t="s">
@@ -6663,24 +6681,27 @@
       <c r="Z9" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="10" spans="1:26">
+      <c r="AA9" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27">
       <c r="A10" t="s">
         <v>16</v>
       </c>
-      <c r="E10" t="s">
-        <v>256</v>
-      </c>
-      <c r="L10" t="s">
-        <v>256</v>
-      </c>
-      <c r="O10" t="s">
+      <c r="D10" t="s">
+        <v>256</v>
+      </c>
+      <c r="F10" t="s">
+        <v>256</v>
+      </c>
+      <c r="M10" t="s">
         <v>256</v>
       </c>
       <c r="P10" t="s">
         <v>256</v>
       </c>
-      <c r="S10" t="s">
+      <c r="Q10" t="s">
         <v>256</v>
       </c>
       <c r="T10" t="s">
@@ -6689,56 +6710,56 @@
       <c r="U10" t="s">
         <v>256</v>
       </c>
-      <c r="W10" t="s">
+      <c r="V10" t="s">
         <v>256</v>
       </c>
       <c r="X10" t="s">
         <v>256</v>
       </c>
-      <c r="Z10" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26">
+      <c r="Y10" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27">
       <c r="A11" t="s">
         <v>17</v>
       </c>
-      <c r="L11" t="s">
-        <v>256</v>
-      </c>
-      <c r="P11" t="s">
-        <v>256</v>
-      </c>
-      <c r="R11" t="s">
+      <c r="M11" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q11" t="s">
         <v>256</v>
       </c>
       <c r="S11" t="s">
         <v>256</v>
       </c>
-      <c r="U11" t="s">
-        <v>256</v>
-      </c>
-      <c r="W11" t="s">
-        <v>256</v>
-      </c>
-      <c r="Y11" t="s">
+      <c r="T11" t="s">
+        <v>256</v>
+      </c>
+      <c r="V11" t="s">
+        <v>256</v>
+      </c>
+      <c r="X11" t="s">
         <v>256</v>
       </c>
       <c r="Z11" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="12" spans="1:26">
+      <c r="AA11" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27">
       <c r="A12" t="s">
         <v>18</v>
       </c>
-      <c r="D12" t="s">
-        <v>256</v>
-      </c>
-      <c r="F12" t="s">
-        <v>256</v>
-      </c>
-      <c r="H12" t="s">
+      <c r="E12" t="s">
+        <v>256</v>
+      </c>
+      <c r="G12" t="s">
         <v>256</v>
       </c>
       <c r="I12" t="s">
@@ -6747,13 +6768,13 @@
       <c r="J12" t="s">
         <v>256</v>
       </c>
-      <c r="L12" t="s">
-        <v>256</v>
-      </c>
-      <c r="P12" t="s">
-        <v>256</v>
-      </c>
-      <c r="R12" t="s">
+      <c r="K12" t="s">
+        <v>256</v>
+      </c>
+      <c r="M12" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q12" t="s">
         <v>256</v>
       </c>
       <c r="S12" t="s">
@@ -6765,7 +6786,7 @@
       <c r="U12" t="s">
         <v>256</v>
       </c>
-      <c r="W12" t="s">
+      <c r="V12" t="s">
         <v>256</v>
       </c>
       <c r="X12" t="s">
@@ -6777,8 +6798,11 @@
       <c r="Z12" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="13" spans="1:26">
+      <c r="AA12" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -6788,10 +6812,10 @@
       <c r="E13" t="s">
         <v>256</v>
       </c>
-      <c r="L13" t="s">
-        <v>256</v>
-      </c>
-      <c r="N13" t="s">
+      <c r="F13" t="s">
+        <v>256</v>
+      </c>
+      <c r="M13" t="s">
         <v>256</v>
       </c>
       <c r="O13" t="s">
@@ -6800,42 +6824,42 @@
       <c r="P13" t="s">
         <v>256</v>
       </c>
-      <c r="R13" t="s">
+      <c r="Q13" t="s">
         <v>256</v>
       </c>
       <c r="S13" t="s">
         <v>256</v>
       </c>
-      <c r="U13" t="s">
-        <v>256</v>
-      </c>
-      <c r="W13" t="s">
+      <c r="T13" t="s">
+        <v>256</v>
+      </c>
+      <c r="V13" t="s">
         <v>256</v>
       </c>
       <c r="X13" t="s">
         <v>256</v>
       </c>
-      <c r="Z13" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26">
+      <c r="Y13" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27">
       <c r="A14" t="s">
         <v>20</v>
       </c>
       <c r="B14" t="s">
         <v>256</v>
       </c>
-      <c r="D14" t="s">
-        <v>256</v>
-      </c>
-      <c r="L14" t="s">
-        <v>256</v>
-      </c>
-      <c r="P14" t="s">
-        <v>256</v>
-      </c>
-      <c r="R14" t="s">
+      <c r="E14" t="s">
+        <v>256</v>
+      </c>
+      <c r="M14" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q14" t="s">
         <v>256</v>
       </c>
       <c r="S14" t="s">
@@ -6847,7 +6871,7 @@
       <c r="U14" t="s">
         <v>256</v>
       </c>
-      <c r="W14" t="s">
+      <c r="V14" t="s">
         <v>256</v>
       </c>
       <c r="X14" t="s">
@@ -6859,27 +6883,30 @@
       <c r="Z14" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="15" spans="1:26">
+      <c r="AA14" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27">
       <c r="A15" t="s">
         <v>21</v>
       </c>
-      <c r="E15" t="s">
+      <c r="D15" t="s">
         <v>256</v>
       </c>
       <c r="F15" t="s">
         <v>256</v>
       </c>
-      <c r="I15" t="s">
+      <c r="G15" t="s">
         <v>256</v>
       </c>
       <c r="J15" t="s">
         <v>256</v>
       </c>
-      <c r="L15" t="s">
-        <v>256</v>
-      </c>
-      <c r="O15" t="s">
+      <c r="K15" t="s">
+        <v>256</v>
+      </c>
+      <c r="M15" t="s">
         <v>256</v>
       </c>
       <c r="P15" t="s">
@@ -6900,7 +6927,7 @@
       <c r="U15" t="s">
         <v>256</v>
       </c>
-      <c r="W15" t="s">
+      <c r="V15" t="s">
         <v>256</v>
       </c>
       <c r="X15" t="s">
@@ -6912,8 +6939,11 @@
       <c r="Z15" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="16" spans="1:26">
+      <c r="AA15" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -6923,35 +6953,35 @@
       <c r="C16" t="s">
         <v>256</v>
       </c>
-      <c r="E16" t="s">
-        <v>256</v>
-      </c>
       <c r="F16" t="s">
         <v>256</v>
       </c>
-      <c r="P16" t="s">
-        <v>256</v>
-      </c>
-      <c r="R16" t="s">
-        <v>256</v>
-      </c>
-      <c r="T16" t="s">
+      <c r="G16" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>256</v>
+      </c>
+      <c r="S16" t="s">
         <v>256</v>
       </c>
       <c r="U16" t="s">
         <v>256</v>
       </c>
-      <c r="W16" t="s">
+      <c r="V16" t="s">
         <v>256</v>
       </c>
       <c r="X16" t="s">
         <v>256</v>
       </c>
-      <c r="Z16" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="17" spans="1:26">
+      <c r="Y16" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -6964,16 +6994,16 @@
       <c r="F17" t="s">
         <v>256</v>
       </c>
-      <c r="L17" t="s">
-        <v>256</v>
-      </c>
-      <c r="O17" t="s">
+      <c r="G17" t="s">
+        <v>256</v>
+      </c>
+      <c r="M17" t="s">
         <v>256</v>
       </c>
       <c r="P17" t="s">
         <v>256</v>
       </c>
-      <c r="R17" t="s">
+      <c r="Q17" t="s">
         <v>256</v>
       </c>
       <c r="S17" t="s">
@@ -6985,7 +7015,7 @@
       <c r="U17" t="s">
         <v>256</v>
       </c>
-      <c r="W17" t="s">
+      <c r="V17" t="s">
         <v>256</v>
       </c>
       <c r="X17" t="s">
@@ -6997,27 +7027,27 @@
       <c r="Z17" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="18" spans="1:26">
+      <c r="AA17" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27">
       <c r="A18" t="s">
         <v>24</v>
       </c>
       <c r="B18" t="s">
         <v>256</v>
       </c>
-      <c r="F18" t="s">
-        <v>256</v>
-      </c>
-      <c r="I18" t="s">
+      <c r="G18" t="s">
         <v>256</v>
       </c>
       <c r="J18" t="s">
         <v>256</v>
       </c>
-      <c r="L18" t="s">
-        <v>256</v>
-      </c>
-      <c r="P18" t="s">
+      <c r="K18" t="s">
+        <v>256</v>
+      </c>
+      <c r="M18" t="s">
         <v>256</v>
       </c>
       <c r="Q18" t="s">
@@ -7035,65 +7065,65 @@
       <c r="U18" t="s">
         <v>256</v>
       </c>
-      <c r="W18" t="s">
+      <c r="V18" t="s">
         <v>256</v>
       </c>
       <c r="X18" t="s">
         <v>256</v>
       </c>
-      <c r="Z18" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="19" spans="1:26">
+      <c r="Y18" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27">
       <c r="A19" t="s">
         <v>25</v>
       </c>
-      <c r="D19" t="s">
-        <v>256</v>
-      </c>
       <c r="E19" t="s">
         <v>256</v>
       </c>
       <c r="F19" t="s">
         <v>256</v>
       </c>
-      <c r="L19" t="s">
-        <v>256</v>
-      </c>
-      <c r="N19" t="s">
-        <v>256</v>
-      </c>
-      <c r="P19" t="s">
-        <v>256</v>
-      </c>
-      <c r="T19" t="s">
+      <c r="G19" t="s">
+        <v>256</v>
+      </c>
+      <c r="M19" t="s">
+        <v>256</v>
+      </c>
+      <c r="O19" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q19" t="s">
         <v>256</v>
       </c>
       <c r="U19" t="s">
         <v>256</v>
       </c>
-      <c r="W19" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="20" spans="1:26">
+      <c r="V19" t="s">
+        <v>256</v>
+      </c>
+      <c r="X19" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27">
       <c r="A20" t="s">
         <v>26</v>
       </c>
-      <c r="E20" t="s">
-        <v>256</v>
-      </c>
       <c r="F20" t="s">
         <v>256</v>
       </c>
-      <c r="L20" t="s">
-        <v>256</v>
-      </c>
-      <c r="P20" t="s">
-        <v>256</v>
-      </c>
-      <c r="S20" t="s">
+      <c r="G20" t="s">
+        <v>256</v>
+      </c>
+      <c r="M20" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q20" t="s">
         <v>256</v>
       </c>
       <c r="T20" t="s">
@@ -7102,7 +7132,7 @@
       <c r="U20" t="s">
         <v>256</v>
       </c>
-      <c r="W20" t="s">
+      <c r="V20" t="s">
         <v>256</v>
       </c>
       <c r="X20" t="s">
@@ -7114,8 +7144,11 @@
       <c r="Z20" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="21" spans="1:26">
+      <c r="AA20" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -7128,16 +7161,16 @@
       <c r="F21" t="s">
         <v>256</v>
       </c>
-      <c r="H21" t="s">
-        <v>256</v>
-      </c>
-      <c r="J21" t="s">
-        <v>256</v>
-      </c>
-      <c r="L21" t="s">
-        <v>256</v>
-      </c>
-      <c r="N21" t="s">
+      <c r="G21" t="s">
+        <v>256</v>
+      </c>
+      <c r="I21" t="s">
+        <v>256</v>
+      </c>
+      <c r="K21" t="s">
+        <v>256</v>
+      </c>
+      <c r="M21" t="s">
         <v>256</v>
       </c>
       <c r="O21" t="s">
@@ -7161,7 +7194,7 @@
       <c r="U21" t="s">
         <v>256</v>
       </c>
-      <c r="W21" t="s">
+      <c r="V21" t="s">
         <v>256</v>
       </c>
       <c r="X21" t="s">
@@ -7173,21 +7206,24 @@
       <c r="Z21" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="22" spans="1:26">
+      <c r="AA21" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27">
       <c r="A22" t="s">
         <v>29</v>
       </c>
-      <c r="E22" t="s">
-        <v>256</v>
-      </c>
-      <c r="J22" t="s">
-        <v>256</v>
-      </c>
-      <c r="L22" t="s">
-        <v>256</v>
-      </c>
-      <c r="O22" t="s">
+      <c r="D22" t="s">
+        <v>256</v>
+      </c>
+      <c r="F22" t="s">
+        <v>256</v>
+      </c>
+      <c r="K22" t="s">
+        <v>256</v>
+      </c>
+      <c r="M22" t="s">
         <v>256</v>
       </c>
       <c r="P22" t="s">
@@ -7208,7 +7244,7 @@
       <c r="U22" t="s">
         <v>256</v>
       </c>
-      <c r="W22" t="s">
+      <c r="V22" t="s">
         <v>256</v>
       </c>
       <c r="X22" t="s">
@@ -7220,21 +7256,21 @@
       <c r="Z22" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="23" spans="1:26">
+      <c r="AA22" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27">
       <c r="A23" t="s">
         <v>30</v>
       </c>
-      <c r="E23" t="s">
-        <v>256</v>
-      </c>
       <c r="F23" t="s">
         <v>256</v>
       </c>
-      <c r="L23" t="s">
-        <v>256</v>
-      </c>
-      <c r="P23" t="s">
+      <c r="G23" t="s">
+        <v>256</v>
+      </c>
+      <c r="M23" t="s">
         <v>256</v>
       </c>
       <c r="Q23" t="s">
@@ -7267,8 +7303,11 @@
       <c r="Z23" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="24" spans="1:26">
+      <c r="AA23" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -7281,16 +7320,16 @@
       <c r="F24" t="s">
         <v>256</v>
       </c>
-      <c r="H24" t="s">
-        <v>256</v>
-      </c>
-      <c r="J24" t="s">
-        <v>256</v>
-      </c>
-      <c r="L24" t="s">
-        <v>256</v>
-      </c>
-      <c r="N24" t="s">
+      <c r="G24" t="s">
+        <v>256</v>
+      </c>
+      <c r="I24" t="s">
+        <v>256</v>
+      </c>
+      <c r="K24" t="s">
+        <v>256</v>
+      </c>
+      <c r="M24" t="s">
         <v>256</v>
       </c>
       <c r="O24" t="s">
@@ -7299,7 +7338,7 @@
       <c r="P24" t="s">
         <v>256</v>
       </c>
-      <c r="S24" t="s">
+      <c r="Q24" t="s">
         <v>256</v>
       </c>
       <c r="T24" t="s">
@@ -7308,7 +7347,7 @@
       <c r="U24" t="s">
         <v>256</v>
       </c>
-      <c r="W24" t="s">
+      <c r="V24" t="s">
         <v>256</v>
       </c>
       <c r="X24" t="s">
@@ -7320,21 +7359,24 @@
       <c r="Z24" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="25" spans="1:26">
+      <c r="AA24" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27">
       <c r="A25" t="s">
         <v>32</v>
       </c>
-      <c r="E25" t="s">
+      <c r="D25" t="s">
         <v>256</v>
       </c>
       <c r="F25" t="s">
         <v>256</v>
       </c>
-      <c r="L25" t="s">
-        <v>256</v>
-      </c>
-      <c r="O25" t="s">
+      <c r="G25" t="s">
+        <v>256</v>
+      </c>
+      <c r="M25" t="s">
         <v>256</v>
       </c>
       <c r="P25" t="s">
@@ -7355,7 +7397,7 @@
       <c r="U25" t="s">
         <v>256</v>
       </c>
-      <c r="W25" t="s">
+      <c r="V25" t="s">
         <v>256</v>
       </c>
       <c r="X25" t="s">
@@ -7367,8 +7409,11 @@
       <c r="Z25" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="26" spans="1:26">
+      <c r="AA25" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -7381,16 +7426,16 @@
       <c r="F26" t="s">
         <v>256</v>
       </c>
-      <c r="H26" t="s">
-        <v>256</v>
-      </c>
-      <c r="O26" t="s">
+      <c r="G26" t="s">
+        <v>256</v>
+      </c>
+      <c r="I26" t="s">
         <v>256</v>
       </c>
       <c r="P26" t="s">
         <v>256</v>
       </c>
-      <c r="R26" t="s">
+      <c r="Q26" t="s">
         <v>256</v>
       </c>
       <c r="S26" t="s">
@@ -7402,55 +7447,58 @@
       <c r="U26" t="s">
         <v>256</v>
       </c>
-      <c r="W26" t="s">
+      <c r="V26" t="s">
         <v>256</v>
       </c>
       <c r="X26" t="s">
         <v>256</v>
       </c>
-      <c r="Z26" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="27" spans="1:26">
+      <c r="Y26" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27">
       <c r="A27" t="s">
         <v>34</v>
       </c>
       <c r="B27" t="s">
         <v>256</v>
       </c>
-      <c r="F27" t="s">
-        <v>256</v>
-      </c>
-      <c r="I27" t="s">
-        <v>256</v>
-      </c>
-      <c r="L27" t="s">
-        <v>256</v>
-      </c>
-      <c r="N27" t="s">
-        <v>256</v>
-      </c>
-      <c r="P27" t="s">
-        <v>256</v>
-      </c>
-      <c r="T27" t="s">
+      <c r="G27" t="s">
+        <v>256</v>
+      </c>
+      <c r="J27" t="s">
+        <v>256</v>
+      </c>
+      <c r="M27" t="s">
+        <v>256</v>
+      </c>
+      <c r="O27" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q27" t="s">
         <v>256</v>
       </c>
       <c r="U27" t="s">
         <v>256</v>
       </c>
-      <c r="W27" t="s">
-        <v>256</v>
-      </c>
-      <c r="Y27" t="s">
+      <c r="V27" t="s">
+        <v>256</v>
+      </c>
+      <c r="X27" t="s">
         <v>256</v>
       </c>
       <c r="Z27" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="28" spans="1:26">
+      <c r="AA27" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27">
       <c r="A28" t="s">
         <v>35</v>
       </c>
@@ -7460,16 +7508,16 @@
       <c r="D28" t="s">
         <v>256</v>
       </c>
-      <c r="F28" t="s">
-        <v>256</v>
-      </c>
-      <c r="I28" t="s">
-        <v>256</v>
-      </c>
-      <c r="L28" t="s">
-        <v>256</v>
-      </c>
-      <c r="N28" t="s">
+      <c r="E28" t="s">
+        <v>256</v>
+      </c>
+      <c r="G28" t="s">
+        <v>256</v>
+      </c>
+      <c r="J28" t="s">
+        <v>256</v>
+      </c>
+      <c r="M28" t="s">
         <v>256</v>
       </c>
       <c r="O28" t="s">
@@ -7478,7 +7526,7 @@
       <c r="P28" t="s">
         <v>256</v>
       </c>
-      <c r="R28" t="s">
+      <c r="Q28" t="s">
         <v>256</v>
       </c>
       <c r="S28" t="s">
@@ -7490,7 +7538,7 @@
       <c r="U28" t="s">
         <v>256</v>
       </c>
-      <c r="W28" t="s">
+      <c r="V28" t="s">
         <v>256</v>
       </c>
       <c r="X28" t="s">
@@ -7502,21 +7550,21 @@
       <c r="Z28" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="29" spans="1:26">
+      <c r="AA28" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27">
       <c r="A29" t="s">
         <v>36</v>
       </c>
-      <c r="E29" t="s">
-        <v>256</v>
-      </c>
       <c r="F29" t="s">
         <v>256</v>
       </c>
-      <c r="L29" t="s">
-        <v>256</v>
-      </c>
-      <c r="P29" t="s">
+      <c r="G29" t="s">
+        <v>256</v>
+      </c>
+      <c r="M29" t="s">
         <v>256</v>
       </c>
       <c r="Q29" t="s">
@@ -7549,30 +7597,30 @@
       <c r="Z29" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="30" spans="1:26">
+      <c r="AA29" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27">
       <c r="A30" t="s">
         <v>37</v>
       </c>
-      <c r="E30" t="s">
-        <v>256</v>
-      </c>
       <c r="F30" t="s">
         <v>256</v>
       </c>
-      <c r="P30" t="s">
-        <v>256</v>
-      </c>
-      <c r="R30" t="s">
-        <v>256</v>
-      </c>
-      <c r="T30" t="s">
+      <c r="G30" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>256</v>
+      </c>
+      <c r="S30" t="s">
         <v>256</v>
       </c>
       <c r="U30" t="s">
         <v>256</v>
       </c>
-      <c r="W30" t="s">
+      <c r="V30" t="s">
         <v>256</v>
       </c>
       <c r="X30" t="s">
@@ -7581,40 +7629,46 @@
       <c r="Y30" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="31" spans="1:26">
+      <c r="Z30" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27">
       <c r="A31" t="s">
         <v>38</v>
       </c>
-      <c r="E31" t="s">
-        <v>256</v>
-      </c>
-      <c r="L31" t="s">
-        <v>256</v>
-      </c>
-      <c r="O31" t="s">
+      <c r="D31" t="s">
+        <v>256</v>
+      </c>
+      <c r="F31" t="s">
+        <v>256</v>
+      </c>
+      <c r="M31" t="s">
         <v>256</v>
       </c>
       <c r="P31" t="s">
         <v>256</v>
       </c>
-      <c r="R31" t="s">
+      <c r="Q31" t="s">
         <v>256</v>
       </c>
       <c r="S31" t="s">
         <v>256</v>
       </c>
-      <c r="U31" t="s">
-        <v>256</v>
-      </c>
-      <c r="W31" t="s">
-        <v>256</v>
-      </c>
-      <c r="Z31" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="32" spans="1:26">
+      <c r="T31" t="s">
+        <v>256</v>
+      </c>
+      <c r="V31" t="s">
+        <v>256</v>
+      </c>
+      <c r="X31" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27">
       <c r="A32" t="s">
         <v>39</v>
       </c>
@@ -7627,19 +7681,19 @@
       <c r="F32" t="s">
         <v>256</v>
       </c>
-      <c r="J32" t="s">
-        <v>256</v>
-      </c>
-      <c r="L32" t="s">
-        <v>256</v>
-      </c>
-      <c r="O32" t="s">
+      <c r="G32" t="s">
+        <v>256</v>
+      </c>
+      <c r="K32" t="s">
+        <v>256</v>
+      </c>
+      <c r="M32" t="s">
         <v>256</v>
       </c>
       <c r="P32" t="s">
         <v>256</v>
       </c>
-      <c r="R32" t="s">
+      <c r="Q32" t="s">
         <v>256</v>
       </c>
       <c r="S32" t="s">
@@ -7651,7 +7705,7 @@
       <c r="U32" t="s">
         <v>256</v>
       </c>
-      <c r="W32" t="s">
+      <c r="V32" t="s">
         <v>256</v>
       </c>
       <c r="X32" t="s">
@@ -7663,36 +7717,39 @@
       <c r="Z32" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="33" spans="1:26">
+      <c r="AA32" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27">
       <c r="A33" t="s">
         <v>40</v>
       </c>
       <c r="B33" t="s">
         <v>256</v>
       </c>
-      <c r="F33" t="s">
-        <v>256</v>
-      </c>
-      <c r="L33" t="s">
-        <v>256</v>
-      </c>
-      <c r="O33" t="s">
+      <c r="D33" t="s">
+        <v>256</v>
+      </c>
+      <c r="G33" t="s">
+        <v>256</v>
+      </c>
+      <c r="M33" t="s">
         <v>256</v>
       </c>
       <c r="P33" t="s">
         <v>256</v>
       </c>
-      <c r="R33" t="s">
+      <c r="Q33" t="s">
         <v>256</v>
       </c>
       <c r="S33" t="s">
         <v>256</v>
       </c>
-      <c r="U33" t="s">
-        <v>256</v>
-      </c>
-      <c r="W33" t="s">
+      <c r="T33" t="s">
+        <v>256</v>
+      </c>
+      <c r="V33" t="s">
         <v>256</v>
       </c>
       <c r="X33" t="s">
@@ -7704,27 +7761,27 @@
       <c r="Z33" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="34" spans="1:26">
+      <c r="AA33" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27">
       <c r="A34" t="s">
         <v>41</v>
       </c>
       <c r="C34" t="s">
         <v>256</v>
       </c>
-      <c r="E34" t="s">
-        <v>256</v>
-      </c>
       <c r="F34" t="s">
         <v>256</v>
       </c>
-      <c r="L34" t="s">
-        <v>256</v>
-      </c>
-      <c r="P34" t="s">
-        <v>256</v>
-      </c>
-      <c r="R34" t="s">
+      <c r="G34" t="s">
+        <v>256</v>
+      </c>
+      <c r="M34" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q34" t="s">
         <v>256</v>
       </c>
       <c r="S34" t="s">
@@ -7736,7 +7793,7 @@
       <c r="U34" t="s">
         <v>256</v>
       </c>
-      <c r="W34" t="s">
+      <c r="V34" t="s">
         <v>256</v>
       </c>
       <c r="X34" t="s">
@@ -7748,24 +7805,24 @@
       <c r="Z34" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="35" spans="1:26">
+      <c r="AA34" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27">
       <c r="A35" t="s">
         <v>42</v>
       </c>
       <c r="B35" t="s">
         <v>256</v>
       </c>
-      <c r="P35" t="s">
-        <v>256</v>
-      </c>
-      <c r="R35" t="s">
-        <v>256</v>
-      </c>
-      <c r="T35" t="s">
-        <v>256</v>
-      </c>
-      <c r="W35" t="s">
+      <c r="Q35" t="s">
+        <v>256</v>
+      </c>
+      <c r="S35" t="s">
+        <v>256</v>
+      </c>
+      <c r="U35" t="s">
         <v>256</v>
       </c>
       <c r="X35" t="s">
@@ -7777,24 +7834,24 @@
       <c r="Z35" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="36" spans="1:26">
+      <c r="AA35" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27">
       <c r="A36" t="s">
         <v>43</v>
       </c>
-      <c r="E36" t="s">
-        <v>256</v>
-      </c>
       <c r="F36" t="s">
         <v>256</v>
       </c>
-      <c r="J36" t="s">
-        <v>256</v>
-      </c>
-      <c r="L36" t="s">
-        <v>256</v>
-      </c>
-      <c r="P36" t="s">
+      <c r="G36" t="s">
+        <v>256</v>
+      </c>
+      <c r="K36" t="s">
+        <v>256</v>
+      </c>
+      <c r="M36" t="s">
         <v>256</v>
       </c>
       <c r="Q36" t="s">
@@ -7803,13 +7860,13 @@
       <c r="R36" t="s">
         <v>256</v>
       </c>
-      <c r="T36" t="s">
+      <c r="S36" t="s">
         <v>256</v>
       </c>
       <c r="U36" t="s">
         <v>256</v>
       </c>
-      <c r="W36" t="s">
+      <c r="V36" t="s">
         <v>256</v>
       </c>
       <c r="X36" t="s">
@@ -7821,8 +7878,11 @@
       <c r="Z36" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="37" spans="1:26">
+      <c r="AA36" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27">
       <c r="A37" t="s">
         <v>44</v>
       </c>
@@ -7832,13 +7892,13 @@
       <c r="E37" t="s">
         <v>256</v>
       </c>
-      <c r="J37" t="s">
-        <v>256</v>
-      </c>
-      <c r="L37" t="s">
-        <v>256</v>
-      </c>
-      <c r="O37" t="s">
+      <c r="F37" t="s">
+        <v>256</v>
+      </c>
+      <c r="K37" t="s">
+        <v>256</v>
+      </c>
+      <c r="M37" t="s">
         <v>256</v>
       </c>
       <c r="P37" t="s">
@@ -7850,7 +7910,7 @@
       <c r="R37" t="s">
         <v>256</v>
       </c>
-      <c r="W37" t="s">
+      <c r="S37" t="s">
         <v>256</v>
       </c>
       <c r="X37" t="s">
@@ -7862,24 +7922,24 @@
       <c r="Z37" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="38" spans="1:26">
+      <c r="AA37" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27">
       <c r="A38" t="s">
         <v>45</v>
       </c>
       <c r="C38" t="s">
         <v>256</v>
       </c>
-      <c r="D38" t="s">
-        <v>256</v>
-      </c>
       <c r="E38" t="s">
         <v>256</v>
       </c>
       <c r="F38" t="s">
         <v>256</v>
       </c>
-      <c r="H38" t="s">
+      <c r="G38" t="s">
         <v>256</v>
       </c>
       <c r="I38" t="s">
@@ -7888,25 +7948,25 @@
       <c r="J38" t="s">
         <v>256</v>
       </c>
-      <c r="L38" t="s">
-        <v>256</v>
-      </c>
-      <c r="N38" t="s">
-        <v>256</v>
-      </c>
-      <c r="P38" t="s">
-        <v>256</v>
-      </c>
-      <c r="R38" t="s">
-        <v>256</v>
-      </c>
-      <c r="T38" t="s">
+      <c r="K38" t="s">
+        <v>256</v>
+      </c>
+      <c r="M38" t="s">
+        <v>256</v>
+      </c>
+      <c r="O38" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>256</v>
+      </c>
+      <c r="S38" t="s">
         <v>256</v>
       </c>
       <c r="U38" t="s">
         <v>256</v>
       </c>
-      <c r="W38" t="s">
+      <c r="V38" t="s">
         <v>256</v>
       </c>
       <c r="X38" t="s">
@@ -7918,8 +7978,11 @@
       <c r="Z38" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="39" spans="1:26">
+      <c r="AA38" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27">
       <c r="A39" t="s">
         <v>46</v>
       </c>
@@ -7929,22 +7992,22 @@
       <c r="D39" t="s">
         <v>256</v>
       </c>
-      <c r="F39" t="s">
-        <v>256</v>
-      </c>
-      <c r="I39" t="s">
+      <c r="E39" t="s">
+        <v>256</v>
+      </c>
+      <c r="G39" t="s">
         <v>256</v>
       </c>
       <c r="J39" t="s">
         <v>256</v>
       </c>
-      <c r="L39" t="s">
+      <c r="K39" t="s">
         <v>256</v>
       </c>
       <c r="M39" t="s">
         <v>256</v>
       </c>
-      <c r="O39" t="s">
+      <c r="N39" t="s">
         <v>256</v>
       </c>
       <c r="P39" t="s">
@@ -7953,7 +8016,7 @@
       <c r="Q39" t="s">
         <v>256</v>
       </c>
-      <c r="S39" t="s">
+      <c r="R39" t="s">
         <v>256</v>
       </c>
       <c r="T39" t="s">
@@ -7962,7 +8025,7 @@
       <c r="U39" t="s">
         <v>256</v>
       </c>
-      <c r="W39" t="s">
+      <c r="V39" t="s">
         <v>256</v>
       </c>
       <c r="X39" t="s">
@@ -7974,32 +8037,32 @@
       <c r="Z39" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="40" spans="1:26">
+      <c r="AA39" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="40" spans="1:27">
       <c r="A40" t="s">
         <v>47</v>
       </c>
-      <c r="P40" t="s">
-        <v>256</v>
-      </c>
-      <c r="W40" t="s">
-        <v>256</v>
-      </c>
-      <c r="Z40" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="41" spans="1:26">
+      <c r="Q40" t="s">
+        <v>256</v>
+      </c>
+      <c r="X40" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA40" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="41" spans="1:27">
       <c r="A41" t="s">
         <v>48</v>
       </c>
       <c r="B41" t="s">
         <v>256</v>
       </c>
-      <c r="F41" t="s">
-        <v>256</v>
-      </c>
-      <c r="P41" t="s">
+      <c r="G41" t="s">
         <v>256</v>
       </c>
       <c r="Q41" t="s">
@@ -8008,13 +8071,13 @@
       <c r="R41" t="s">
         <v>256</v>
       </c>
-      <c r="T41" t="s">
+      <c r="S41" t="s">
         <v>256</v>
       </c>
       <c r="U41" t="s">
         <v>256</v>
       </c>
-      <c r="W41" t="s">
+      <c r="V41" t="s">
         <v>256</v>
       </c>
       <c r="X41" t="s">
@@ -8026,55 +8089,58 @@
       <c r="Z41" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="42" spans="1:26">
+      <c r="AA41" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="42" spans="1:27">
       <c r="A42" t="s">
         <v>49</v>
       </c>
-      <c r="L42" t="s">
-        <v>256</v>
-      </c>
-      <c r="U42" t="s">
-        <v>256</v>
-      </c>
-      <c r="W42" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="43" spans="1:26">
+      <c r="M42" t="s">
+        <v>256</v>
+      </c>
+      <c r="V42" t="s">
+        <v>256</v>
+      </c>
+      <c r="X42" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="43" spans="1:27">
       <c r="A43" t="s">
         <v>51</v>
       </c>
-      <c r="P43" t="s">
-        <v>256</v>
-      </c>
-      <c r="R43" t="s">
-        <v>256</v>
-      </c>
-      <c r="U43" t="s">
-        <v>256</v>
-      </c>
-      <c r="W43" t="s">
-        <v>256</v>
-      </c>
-      <c r="Z43" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="44" spans="1:26">
+      <c r="Q43" t="s">
+        <v>256</v>
+      </c>
+      <c r="S43" t="s">
+        <v>256</v>
+      </c>
+      <c r="V43" t="s">
+        <v>256</v>
+      </c>
+      <c r="X43" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA43" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="44" spans="1:27">
       <c r="A44" t="s">
         <v>52</v>
       </c>
-      <c r="E44" t="s">
+      <c r="D44" t="s">
         <v>256</v>
       </c>
       <c r="F44" t="s">
         <v>256</v>
       </c>
-      <c r="L44" t="s">
-        <v>256</v>
-      </c>
-      <c r="N44" t="s">
+      <c r="G44" t="s">
+        <v>256</v>
+      </c>
+      <c r="M44" t="s">
         <v>256</v>
       </c>
       <c r="O44" t="s">
@@ -8083,7 +8149,7 @@
       <c r="P44" t="s">
         <v>256</v>
       </c>
-      <c r="R44" t="s">
+      <c r="Q44" t="s">
         <v>256</v>
       </c>
       <c r="S44" t="s">
@@ -8095,7 +8161,7 @@
       <c r="U44" t="s">
         <v>256</v>
       </c>
-      <c r="W44" t="s">
+      <c r="V44" t="s">
         <v>256</v>
       </c>
       <c r="X44" t="s">
@@ -8107,53 +8173,53 @@
       <c r="Z44" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="45" spans="1:26">
+      <c r="AA44" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="45" spans="1:27">
       <c r="A45" t="s">
         <v>53</v>
       </c>
-      <c r="P45" t="s">
-        <v>256</v>
-      </c>
-      <c r="R45" t="s">
-        <v>256</v>
-      </c>
-      <c r="U45" t="s">
-        <v>256</v>
-      </c>
-      <c r="W45" t="s">
-        <v>256</v>
-      </c>
-      <c r="Z45" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="46" spans="1:26">
+      <c r="Q45" t="s">
+        <v>256</v>
+      </c>
+      <c r="S45" t="s">
+        <v>256</v>
+      </c>
+      <c r="V45" t="s">
+        <v>256</v>
+      </c>
+      <c r="X45" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="46" spans="1:27">
       <c r="A46" t="s">
         <v>54</v>
       </c>
-      <c r="E46" t="s">
-        <v>256</v>
-      </c>
-      <c r="J46" t="s">
-        <v>256</v>
-      </c>
-      <c r="L46" t="s">
-        <v>256</v>
-      </c>
-      <c r="P46" t="s">
-        <v>256</v>
-      </c>
-      <c r="R46" t="s">
-        <v>256</v>
-      </c>
-      <c r="T46" t="s">
+      <c r="F46" t="s">
+        <v>256</v>
+      </c>
+      <c r="K46" t="s">
+        <v>256</v>
+      </c>
+      <c r="M46" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>256</v>
+      </c>
+      <c r="S46" t="s">
         <v>256</v>
       </c>
       <c r="U46" t="s">
         <v>256</v>
       </c>
-      <c r="W46" t="s">
+      <c r="V46" t="s">
         <v>256</v>
       </c>
       <c r="X46" t="s">
@@ -8165,24 +8231,27 @@
       <c r="Z46" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="47" spans="1:26">
+      <c r="AA46" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="47" spans="1:27">
       <c r="A47" t="s">
         <v>55</v>
       </c>
-      <c r="E47" t="s">
+      <c r="D47" t="s">
         <v>256</v>
       </c>
       <c r="F47" t="s">
         <v>256</v>
       </c>
-      <c r="I47" t="s">
-        <v>256</v>
-      </c>
-      <c r="L47" t="s">
-        <v>256</v>
-      </c>
-      <c r="N47" t="s">
+      <c r="G47" t="s">
+        <v>256</v>
+      </c>
+      <c r="J47" t="s">
+        <v>256</v>
+      </c>
+      <c r="M47" t="s">
         <v>256</v>
       </c>
       <c r="O47" t="s">
@@ -8191,7 +8260,7 @@
       <c r="P47" t="s">
         <v>256</v>
       </c>
-      <c r="R47" t="s">
+      <c r="Q47" t="s">
         <v>256</v>
       </c>
       <c r="S47" t="s">
@@ -8203,7 +8272,7 @@
       <c r="U47" t="s">
         <v>256</v>
       </c>
-      <c r="W47" t="s">
+      <c r="V47" t="s">
         <v>256</v>
       </c>
       <c r="X47" t="s">
@@ -8215,30 +8284,30 @@
       <c r="Z47" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="48" spans="1:26">
+      <c r="AA47" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="48" spans="1:27">
       <c r="A48" t="s">
         <v>56</v>
       </c>
       <c r="B48" t="s">
         <v>256</v>
       </c>
-      <c r="L48" t="s">
-        <v>256</v>
-      </c>
-      <c r="P48" t="s">
-        <v>256</v>
-      </c>
-      <c r="R48" t="s">
+      <c r="M48" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q48" t="s">
         <v>256</v>
       </c>
       <c r="S48" t="s">
         <v>256</v>
       </c>
-      <c r="U48" t="s">
-        <v>256</v>
-      </c>
-      <c r="W48" t="s">
+      <c r="T48" t="s">
+        <v>256</v>
+      </c>
+      <c r="V48" t="s">
         <v>256</v>
       </c>
       <c r="X48" t="s">
@@ -8250,27 +8319,27 @@
       <c r="Z48" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="49" spans="1:26">
+      <c r="AA48" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="49" spans="1:27">
       <c r="A49" t="s">
         <v>57</v>
       </c>
       <c r="C49" t="s">
         <v>256</v>
       </c>
-      <c r="E49" t="s">
-        <v>256</v>
-      </c>
       <c r="F49" t="s">
         <v>256</v>
       </c>
-      <c r="L49" t="s">
-        <v>256</v>
-      </c>
-      <c r="N49" t="s">
-        <v>256</v>
-      </c>
-      <c r="P49" t="s">
+      <c r="G49" t="s">
+        <v>256</v>
+      </c>
+      <c r="M49" t="s">
+        <v>256</v>
+      </c>
+      <c r="O49" t="s">
         <v>256</v>
       </c>
       <c r="Q49" t="s">
@@ -8288,7 +8357,7 @@
       <c r="U49" t="s">
         <v>256</v>
       </c>
-      <c r="W49" t="s">
+      <c r="V49" t="s">
         <v>256</v>
       </c>
       <c r="X49" t="s">
@@ -8300,8 +8369,11 @@
       <c r="Z49" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="50" spans="1:26">
+      <c r="AA49" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="50" spans="1:27">
       <c r="A50" t="s">
         <v>58</v>
       </c>
@@ -8314,7 +8386,7 @@
       <c r="F50" t="s">
         <v>256</v>
       </c>
-      <c r="H50" t="s">
+      <c r="G50" t="s">
         <v>256</v>
       </c>
       <c r="I50" t="s">
@@ -8323,25 +8395,25 @@
       <c r="J50" t="s">
         <v>256</v>
       </c>
-      <c r="L50" t="s">
-        <v>256</v>
-      </c>
-      <c r="O50" t="s">
+      <c r="K50" t="s">
+        <v>256</v>
+      </c>
+      <c r="M50" t="s">
         <v>256</v>
       </c>
       <c r="P50" t="s">
         <v>256</v>
       </c>
-      <c r="R50" t="s">
-        <v>256</v>
-      </c>
-      <c r="T50" t="s">
+      <c r="Q50" t="s">
+        <v>256</v>
+      </c>
+      <c r="S50" t="s">
         <v>256</v>
       </c>
       <c r="U50" t="s">
         <v>256</v>
       </c>
-      <c r="W50" t="s">
+      <c r="V50" t="s">
         <v>256</v>
       </c>
       <c r="X50" t="s">
@@ -8353,8 +8425,11 @@
       <c r="Z50" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="51" spans="1:26">
+      <c r="AA50" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="51" spans="1:27">
       <c r="A51" t="s">
         <v>59</v>
       </c>
@@ -8367,19 +8442,19 @@
       <c r="F51" t="s">
         <v>256</v>
       </c>
-      <c r="J51" t="s">
-        <v>256</v>
-      </c>
-      <c r="L51" t="s">
-        <v>256</v>
-      </c>
-      <c r="O51" t="s">
+      <c r="G51" t="s">
+        <v>256</v>
+      </c>
+      <c r="K51" t="s">
+        <v>256</v>
+      </c>
+      <c r="M51" t="s">
         <v>256</v>
       </c>
       <c r="P51" t="s">
         <v>256</v>
       </c>
-      <c r="R51" t="s">
+      <c r="Q51" t="s">
         <v>256</v>
       </c>
       <c r="S51" t="s">
@@ -8391,7 +8466,7 @@
       <c r="U51" t="s">
         <v>256</v>
       </c>
-      <c r="W51" t="s">
+      <c r="V51" t="s">
         <v>256</v>
       </c>
       <c r="X51" t="s">
@@ -8403,18 +8478,18 @@
       <c r="Z51" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="52" spans="1:26">
+      <c r="AA51" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="52" spans="1:27">
       <c r="A52" t="s">
         <v>60</v>
       </c>
       <c r="B52" t="s">
         <v>256</v>
       </c>
-      <c r="L52" t="s">
-        <v>256</v>
-      </c>
-      <c r="P52" t="s">
+      <c r="M52" t="s">
         <v>256</v>
       </c>
       <c r="Q52" t="s">
@@ -8429,7 +8504,7 @@
       <c r="T52" t="s">
         <v>256</v>
       </c>
-      <c r="W52" t="s">
+      <c r="U52" t="s">
         <v>256</v>
       </c>
       <c r="X52" t="s">
@@ -8441,24 +8516,27 @@
       <c r="Z52" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="53" spans="1:26">
+      <c r="AA52" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="53" spans="1:27">
       <c r="A53" t="s">
         <v>61</v>
       </c>
       <c r="C53" t="s">
         <v>256</v>
       </c>
-      <c r="E53" t="s">
+      <c r="D53" t="s">
         <v>256</v>
       </c>
       <c r="F53" t="s">
         <v>256</v>
       </c>
-      <c r="L53" t="s">
-        <v>256</v>
-      </c>
-      <c r="O53" t="s">
+      <c r="G53" t="s">
+        <v>256</v>
+      </c>
+      <c r="M53" t="s">
         <v>256</v>
       </c>
       <c r="P53" t="s">
@@ -8479,7 +8557,7 @@
       <c r="U53" t="s">
         <v>256</v>
       </c>
-      <c r="W53" t="s">
+      <c r="V53" t="s">
         <v>256</v>
       </c>
       <c r="X53" t="s">
@@ -8491,27 +8569,30 @@
       <c r="Z53" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="54" spans="1:26">
+      <c r="AA53" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="54" spans="1:27">
       <c r="A54" t="s">
         <v>62</v>
       </c>
-      <c r="E54" t="s">
+      <c r="D54" t="s">
         <v>256</v>
       </c>
       <c r="F54" t="s">
         <v>256</v>
       </c>
-      <c r="J54" t="s">
-        <v>256</v>
-      </c>
-      <c r="O54" t="s">
+      <c r="G54" t="s">
+        <v>256</v>
+      </c>
+      <c r="K54" t="s">
         <v>256</v>
       </c>
       <c r="P54" t="s">
         <v>256</v>
       </c>
-      <c r="S54" t="s">
+      <c r="Q54" t="s">
         <v>256</v>
       </c>
       <c r="T54" t="s">
@@ -8520,36 +8601,36 @@
       <c r="U54" t="s">
         <v>256</v>
       </c>
-      <c r="W54" t="s">
+      <c r="V54" t="s">
         <v>256</v>
       </c>
       <c r="X54" t="s">
         <v>256</v>
       </c>
-      <c r="Z54" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="55" spans="1:26">
+      <c r="Y54" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA54" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="55" spans="1:27">
       <c r="A55" t="s">
         <v>64</v>
       </c>
-      <c r="E55" t="s">
-        <v>256</v>
-      </c>
       <c r="F55" t="s">
         <v>256</v>
       </c>
-      <c r="P55" t="s">
-        <v>256</v>
-      </c>
-      <c r="T55" t="s">
+      <c r="G55" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q55" t="s">
         <v>256</v>
       </c>
       <c r="U55" t="s">
         <v>256</v>
       </c>
-      <c r="W55" t="s">
+      <c r="V55" t="s">
         <v>256</v>
       </c>
       <c r="X55" t="s">
@@ -8561,24 +8642,24 @@
       <c r="Z55" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="56" spans="1:26">
+      <c r="AA55" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="56" spans="1:27">
       <c r="A56" t="s">
         <v>65</v>
       </c>
       <c r="B56" t="s">
         <v>256</v>
       </c>
-      <c r="F56" t="s">
-        <v>256</v>
-      </c>
-      <c r="L56" t="s">
-        <v>256</v>
-      </c>
-      <c r="P56" t="s">
-        <v>256</v>
-      </c>
-      <c r="R56" t="s">
+      <c r="G56" t="s">
+        <v>256</v>
+      </c>
+      <c r="M56" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q56" t="s">
         <v>256</v>
       </c>
       <c r="S56" t="s">
@@ -8590,7 +8671,7 @@
       <c r="U56" t="s">
         <v>256</v>
       </c>
-      <c r="W56" t="s">
+      <c r="V56" t="s">
         <v>256</v>
       </c>
       <c r="X56" t="s">
@@ -8602,8 +8683,11 @@
       <c r="Z56" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="57" spans="1:26">
+      <c r="AA56" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="57" spans="1:27">
       <c r="A57" t="s">
         <v>66</v>
       </c>
@@ -8616,10 +8700,10 @@
       <c r="F57" t="s">
         <v>256</v>
       </c>
-      <c r="L57" t="s">
-        <v>256</v>
-      </c>
-      <c r="N57" t="s">
+      <c r="G57" t="s">
+        <v>256</v>
+      </c>
+      <c r="M57" t="s">
         <v>256</v>
       </c>
       <c r="O57" t="s">
@@ -8628,16 +8712,16 @@
       <c r="P57" t="s">
         <v>256</v>
       </c>
-      <c r="R57" t="s">
-        <v>256</v>
-      </c>
-      <c r="T57" t="s">
+      <c r="Q57" t="s">
+        <v>256</v>
+      </c>
+      <c r="S57" t="s">
         <v>256</v>
       </c>
       <c r="U57" t="s">
         <v>256</v>
       </c>
-      <c r="W57" t="s">
+      <c r="V57" t="s">
         <v>256</v>
       </c>
       <c r="X57" t="s">
@@ -8649,8 +8733,11 @@
       <c r="Z57" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="58" spans="1:26">
+      <c r="AA57" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="58" spans="1:27">
       <c r="A58" t="s">
         <v>67</v>
       </c>
@@ -8660,47 +8747,47 @@
       <c r="C58" t="s">
         <v>256</v>
       </c>
-      <c r="D58" t="s">
-        <v>256</v>
-      </c>
       <c r="E58" t="s">
         <v>256</v>
       </c>
       <c r="F58" t="s">
         <v>256</v>
       </c>
-      <c r="H58" t="s">
+      <c r="G58" t="s">
         <v>256</v>
       </c>
       <c r="I58" t="s">
         <v>256</v>
       </c>
-      <c r="L58" t="s">
-        <v>256</v>
-      </c>
-      <c r="P58" t="s">
-        <v>256</v>
-      </c>
-      <c r="R58" t="s">
-        <v>256</v>
-      </c>
-      <c r="T58" t="s">
+      <c r="J58" t="s">
+        <v>256</v>
+      </c>
+      <c r="M58" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>256</v>
+      </c>
+      <c r="S58" t="s">
         <v>256</v>
       </c>
       <c r="U58" t="s">
         <v>256</v>
       </c>
-      <c r="W58" t="s">
+      <c r="V58" t="s">
         <v>256</v>
       </c>
       <c r="X58" t="s">
         <v>256</v>
       </c>
-      <c r="Z58" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="59" spans="1:26">
+      <c r="Y58" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA58" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="59" spans="1:27">
       <c r="A59" t="s">
         <v>68</v>
       </c>
@@ -8716,7 +8803,7 @@
       <c r="F59" t="s">
         <v>256</v>
       </c>
-      <c r="H59" t="s">
+      <c r="G59" t="s">
         <v>256</v>
       </c>
       <c r="I59" t="s">
@@ -8725,16 +8812,16 @@
       <c r="J59" t="s">
         <v>256</v>
       </c>
-      <c r="L59" t="s">
-        <v>256</v>
-      </c>
-      <c r="O59" t="s">
+      <c r="K59" t="s">
+        <v>256</v>
+      </c>
+      <c r="M59" t="s">
         <v>256</v>
       </c>
       <c r="P59" t="s">
         <v>256</v>
       </c>
-      <c r="S59" t="s">
+      <c r="Q59" t="s">
         <v>256</v>
       </c>
       <c r="T59" t="s">
@@ -8743,7 +8830,7 @@
       <c r="U59" t="s">
         <v>256</v>
       </c>
-      <c r="W59" t="s">
+      <c r="V59" t="s">
         <v>256</v>
       </c>
       <c r="X59" t="s">
@@ -8755,30 +8842,30 @@
       <c r="Z59" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="60" spans="1:26">
+      <c r="AA59" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="60" spans="1:27">
       <c r="A60" t="s">
         <v>69</v>
       </c>
-      <c r="E60" t="s">
-        <v>256</v>
-      </c>
       <c r="F60" t="s">
         <v>256</v>
       </c>
-      <c r="H60" t="s">
-        <v>256</v>
-      </c>
-      <c r="J60" t="s">
-        <v>256</v>
-      </c>
-      <c r="L60" t="s">
-        <v>256</v>
-      </c>
-      <c r="P60" t="s">
-        <v>256</v>
-      </c>
-      <c r="R60" t="s">
+      <c r="G60" t="s">
+        <v>256</v>
+      </c>
+      <c r="I60" t="s">
+        <v>256</v>
+      </c>
+      <c r="K60" t="s">
+        <v>256</v>
+      </c>
+      <c r="M60" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q60" t="s">
         <v>256</v>
       </c>
       <c r="S60" t="s">
@@ -8790,7 +8877,7 @@
       <c r="U60" t="s">
         <v>256</v>
       </c>
-      <c r="W60" t="s">
+      <c r="V60" t="s">
         <v>256</v>
       </c>
       <c r="X60" t="s">
@@ -8802,8 +8889,11 @@
       <c r="Z60" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="61" spans="1:26">
+      <c r="AA60" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="61" spans="1:27">
       <c r="A61" t="s">
         <v>70</v>
       </c>
@@ -8819,7 +8909,7 @@
       <c r="F61" t="s">
         <v>256</v>
       </c>
-      <c r="H61" t="s">
+      <c r="G61" t="s">
         <v>256</v>
       </c>
       <c r="I61" t="s">
@@ -8828,16 +8918,16 @@
       <c r="J61" t="s">
         <v>256</v>
       </c>
-      <c r="L61" t="s">
-        <v>256</v>
-      </c>
-      <c r="O61" t="s">
+      <c r="K61" t="s">
+        <v>256</v>
+      </c>
+      <c r="M61" t="s">
         <v>256</v>
       </c>
       <c r="P61" t="s">
         <v>256</v>
       </c>
-      <c r="S61" t="s">
+      <c r="Q61" t="s">
         <v>256</v>
       </c>
       <c r="T61" t="s">
@@ -8846,17 +8936,20 @@
       <c r="U61" t="s">
         <v>256</v>
       </c>
-      <c r="W61" t="s">
+      <c r="V61" t="s">
         <v>256</v>
       </c>
       <c r="X61" t="s">
         <v>256</v>
       </c>
-      <c r="Z61" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="62" spans="1:26">
+      <c r="Y61" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA61" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="62" spans="1:27">
       <c r="A62" t="s">
         <v>71</v>
       </c>
@@ -8869,34 +8962,34 @@
       <c r="D62" t="s">
         <v>256</v>
       </c>
-      <c r="F62" t="s">
-        <v>256</v>
-      </c>
-      <c r="H62" t="s">
-        <v>256</v>
-      </c>
-      <c r="J62" t="s">
-        <v>256</v>
-      </c>
-      <c r="L62" t="s">
-        <v>256</v>
-      </c>
-      <c r="O62" t="s">
+      <c r="E62" t="s">
+        <v>256</v>
+      </c>
+      <c r="G62" t="s">
+        <v>256</v>
+      </c>
+      <c r="I62" t="s">
+        <v>256</v>
+      </c>
+      <c r="K62" t="s">
+        <v>256</v>
+      </c>
+      <c r="M62" t="s">
         <v>256</v>
       </c>
       <c r="P62" t="s">
         <v>256</v>
       </c>
-      <c r="R62" t="s">
-        <v>256</v>
-      </c>
-      <c r="T62" t="s">
+      <c r="Q62" t="s">
+        <v>256</v>
+      </c>
+      <c r="S62" t="s">
         <v>256</v>
       </c>
       <c r="U62" t="s">
         <v>256</v>
       </c>
-      <c r="W62" t="s">
+      <c r="V62" t="s">
         <v>256</v>
       </c>
       <c r="X62" t="s">
@@ -8908,27 +9001,30 @@
       <c r="Z62" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="63" spans="1:26">
+      <c r="AA62" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="63" spans="1:27">
       <c r="A63" t="s">
         <v>72</v>
       </c>
-      <c r="E63" t="s">
+      <c r="D63" t="s">
         <v>256</v>
       </c>
       <c r="F63" t="s">
         <v>256</v>
       </c>
-      <c r="L63" t="s">
-        <v>256</v>
-      </c>
-      <c r="O63" t="s">
+      <c r="G63" t="s">
+        <v>256</v>
+      </c>
+      <c r="M63" t="s">
         <v>256</v>
       </c>
       <c r="P63" t="s">
         <v>256</v>
       </c>
-      <c r="R63" t="s">
+      <c r="Q63" t="s">
         <v>256</v>
       </c>
       <c r="S63" t="s">
@@ -8940,7 +9036,7 @@
       <c r="U63" t="s">
         <v>256</v>
       </c>
-      <c r="W63" t="s">
+      <c r="V63" t="s">
         <v>256</v>
       </c>
       <c r="X63" t="s">
@@ -8952,21 +9048,24 @@
       <c r="Z63" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="64" spans="1:26">
+      <c r="AA63" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="64" spans="1:27">
       <c r="A64" t="s">
         <v>73</v>
       </c>
-      <c r="E64" t="s">
+      <c r="D64" t="s">
         <v>256</v>
       </c>
       <c r="F64" t="s">
         <v>256</v>
       </c>
-      <c r="L64" t="s">
-        <v>256</v>
-      </c>
-      <c r="N64" t="s">
+      <c r="G64" t="s">
+        <v>256</v>
+      </c>
+      <c r="M64" t="s">
         <v>256</v>
       </c>
       <c r="O64" t="s">
@@ -8975,7 +9074,7 @@
       <c r="P64" t="s">
         <v>256</v>
       </c>
-      <c r="S64" t="s">
+      <c r="Q64" t="s">
         <v>256</v>
       </c>
       <c r="T64" t="s">
@@ -8984,7 +9083,7 @@
       <c r="U64" t="s">
         <v>256</v>
       </c>
-      <c r="W64" t="s">
+      <c r="V64" t="s">
         <v>256</v>
       </c>
       <c r="X64" t="s">
@@ -8996,21 +9095,24 @@
       <c r="Z64" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="65" spans="1:26">
+      <c r="AA64" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="65" spans="1:27">
       <c r="A65" t="s">
         <v>74</v>
       </c>
       <c r="B65" t="s">
         <v>256</v>
       </c>
-      <c r="J65" t="s">
-        <v>256</v>
-      </c>
-      <c r="L65" t="s">
-        <v>256</v>
-      </c>
-      <c r="O65" t="s">
+      <c r="D65" t="s">
+        <v>256</v>
+      </c>
+      <c r="K65" t="s">
+        <v>256</v>
+      </c>
+      <c r="M65" t="s">
         <v>256</v>
       </c>
       <c r="P65" t="s">
@@ -9022,40 +9124,46 @@
       <c r="R65" t="s">
         <v>256</v>
       </c>
-      <c r="U65" t="s">
-        <v>256</v>
-      </c>
-      <c r="W65" t="s">
+      <c r="S65" t="s">
+        <v>256</v>
+      </c>
+      <c r="V65" t="s">
         <v>256</v>
       </c>
       <c r="X65" t="s">
         <v>256</v>
       </c>
-      <c r="Z65" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="66" spans="1:26">
+      <c r="Y65" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA65" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="66" spans="1:27">
       <c r="A66" t="s">
         <v>75</v>
       </c>
-      <c r="O66" t="s">
+      <c r="D66" t="s">
         <v>256</v>
       </c>
       <c r="P66" t="s">
         <v>256</v>
       </c>
-      <c r="R66" t="s">
-        <v>256</v>
-      </c>
-      <c r="W66" t="s">
-        <v>256</v>
-      </c>
-      <c r="Z66" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="67" spans="1:26">
+      <c r="Q66" t="s">
+        <v>256</v>
+      </c>
+      <c r="S66" t="s">
+        <v>256</v>
+      </c>
+      <c r="X66" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA66" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="67" spans="1:27">
       <c r="A67" t="s">
         <v>76</v>
       </c>
@@ -9065,10 +9173,10 @@
       <c r="D67" t="s">
         <v>256</v>
       </c>
-      <c r="F67" t="s">
-        <v>256</v>
-      </c>
-      <c r="H67" t="s">
+      <c r="E67" t="s">
+        <v>256</v>
+      </c>
+      <c r="G67" t="s">
         <v>256</v>
       </c>
       <c r="I67" t="s">
@@ -9077,16 +9185,16 @@
       <c r="J67" t="s">
         <v>256</v>
       </c>
-      <c r="L67" t="s">
-        <v>256</v>
-      </c>
-      <c r="O67" t="s">
+      <c r="K67" t="s">
+        <v>256</v>
+      </c>
+      <c r="M67" t="s">
         <v>256</v>
       </c>
       <c r="P67" t="s">
         <v>256</v>
       </c>
-      <c r="S67" t="s">
+      <c r="Q67" t="s">
         <v>256</v>
       </c>
       <c r="T67" t="s">
@@ -9095,7 +9203,7 @@
       <c r="U67" t="s">
         <v>256</v>
       </c>
-      <c r="W67" t="s">
+      <c r="V67" t="s">
         <v>256</v>
       </c>
       <c r="X67" t="s">
@@ -9107,8 +9215,11 @@
       <c r="Z67" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="68" spans="1:26">
+      <c r="AA67" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="68" spans="1:27">
       <c r="A68" t="s">
         <v>78</v>
       </c>
@@ -9118,22 +9229,22 @@
       <c r="D68" t="s">
         <v>256</v>
       </c>
-      <c r="F68" t="s">
-        <v>256</v>
-      </c>
-      <c r="H68" t="s">
-        <v>256</v>
-      </c>
-      <c r="L68" t="s">
-        <v>256</v>
-      </c>
-      <c r="O68" t="s">
+      <c r="E68" t="s">
+        <v>256</v>
+      </c>
+      <c r="G68" t="s">
+        <v>256</v>
+      </c>
+      <c r="I68" t="s">
+        <v>256</v>
+      </c>
+      <c r="M68" t="s">
         <v>256</v>
       </c>
       <c r="P68" t="s">
         <v>256</v>
       </c>
-      <c r="S68" t="s">
+      <c r="Q68" t="s">
         <v>256</v>
       </c>
       <c r="T68" t="s">
@@ -9142,7 +9253,7 @@
       <c r="U68" t="s">
         <v>256</v>
       </c>
-      <c r="W68" t="s">
+      <c r="V68" t="s">
         <v>256</v>
       </c>
       <c r="X68" t="s">
@@ -9154,30 +9265,30 @@
       <c r="Z68" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="69" spans="1:26">
+      <c r="AA68" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="69" spans="1:27">
       <c r="A69" t="s">
         <v>79</v>
       </c>
       <c r="B69" t="s">
         <v>256</v>
       </c>
-      <c r="D69" t="s">
-        <v>256</v>
-      </c>
       <c r="E69" t="s">
         <v>256</v>
       </c>
-      <c r="H69" t="s">
-        <v>256</v>
-      </c>
-      <c r="J69" t="s">
-        <v>256</v>
-      </c>
-      <c r="P69" t="s">
-        <v>256</v>
-      </c>
-      <c r="R69" t="s">
+      <c r="F69" t="s">
+        <v>256</v>
+      </c>
+      <c r="I69" t="s">
+        <v>256</v>
+      </c>
+      <c r="K69" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q69" t="s">
         <v>256</v>
       </c>
       <c r="S69" t="s">
@@ -9189,37 +9300,40 @@
       <c r="U69" t="s">
         <v>256</v>
       </c>
-      <c r="X69" t="s">
-        <v>256</v>
-      </c>
-      <c r="Z69" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="70" spans="1:26">
+      <c r="V69" t="s">
+        <v>256</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA69" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="70" spans="1:27">
       <c r="A70" t="s">
         <v>81</v>
       </c>
-      <c r="L70" t="s">
-        <v>256</v>
-      </c>
-      <c r="P70" t="s">
-        <v>256</v>
-      </c>
-      <c r="R70" t="s">
-        <v>256</v>
-      </c>
-      <c r="U70" t="s">
-        <v>256</v>
-      </c>
-      <c r="Y70" t="s">
+      <c r="M70" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>256</v>
+      </c>
+      <c r="S70" t="s">
+        <v>256</v>
+      </c>
+      <c r="V70" t="s">
         <v>256</v>
       </c>
       <c r="Z70" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="71" spans="1:26">
+      <c r="AA70" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="71" spans="1:27">
       <c r="A71" t="s">
         <v>82</v>
       </c>
@@ -9235,19 +9349,19 @@
       <c r="F71" t="s">
         <v>256</v>
       </c>
-      <c r="J71" t="s">
-        <v>256</v>
-      </c>
-      <c r="L71" t="s">
-        <v>256</v>
-      </c>
-      <c r="O71" t="s">
+      <c r="G71" t="s">
+        <v>256</v>
+      </c>
+      <c r="K71" t="s">
+        <v>256</v>
+      </c>
+      <c r="M71" t="s">
         <v>256</v>
       </c>
       <c r="P71" t="s">
         <v>256</v>
       </c>
-      <c r="R71" t="s">
+      <c r="Q71" t="s">
         <v>256</v>
       </c>
       <c r="S71" t="s">
@@ -9259,7 +9373,7 @@
       <c r="U71" t="s">
         <v>256</v>
       </c>
-      <c r="W71" t="s">
+      <c r="V71" t="s">
         <v>256</v>
       </c>
       <c r="X71" t="s">
@@ -9271,8 +9385,11 @@
       <c r="Z71" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="72" spans="1:26">
+      <c r="AA71" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="72" spans="1:27">
       <c r="A72" t="s">
         <v>83</v>
       </c>
@@ -9288,19 +9405,19 @@
       <c r="F72" t="s">
         <v>256</v>
       </c>
-      <c r="I72" t="s">
-        <v>256</v>
-      </c>
-      <c r="L72" t="s">
-        <v>256</v>
-      </c>
-      <c r="O72" t="s">
+      <c r="G72" t="s">
+        <v>256</v>
+      </c>
+      <c r="J72" t="s">
+        <v>256</v>
+      </c>
+      <c r="M72" t="s">
         <v>256</v>
       </c>
       <c r="P72" t="s">
         <v>256</v>
       </c>
-      <c r="R72" t="s">
+      <c r="Q72" t="s">
         <v>256</v>
       </c>
       <c r="S72" t="s">
@@ -9312,7 +9429,7 @@
       <c r="U72" t="s">
         <v>256</v>
       </c>
-      <c r="W72" t="s">
+      <c r="V72" t="s">
         <v>256</v>
       </c>
       <c r="X72" t="s">
@@ -9324,21 +9441,21 @@
       <c r="Z72" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="73" spans="1:26">
+      <c r="AA72" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="73" spans="1:27">
       <c r="A73" t="s">
         <v>84</v>
       </c>
-      <c r="E73" t="s">
-        <v>256</v>
-      </c>
       <c r="F73" t="s">
         <v>256</v>
       </c>
-      <c r="L73" t="s">
-        <v>256</v>
-      </c>
-      <c r="P73" t="s">
+      <c r="G73" t="s">
+        <v>256</v>
+      </c>
+      <c r="M73" t="s">
         <v>256</v>
       </c>
       <c r="Q73" t="s">
@@ -9356,7 +9473,7 @@
       <c r="U73" t="s">
         <v>256</v>
       </c>
-      <c r="W73" t="s">
+      <c r="V73" t="s">
         <v>256</v>
       </c>
       <c r="X73" t="s">
@@ -9368,27 +9485,30 @@
       <c r="Z73" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="74" spans="1:26">
+      <c r="AA73" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="74" spans="1:27">
       <c r="A74" t="s">
         <v>85</v>
       </c>
-      <c r="E74" t="s">
+      <c r="D74" t="s">
         <v>256</v>
       </c>
       <c r="F74" t="s">
         <v>256</v>
       </c>
-      <c r="L74" t="s">
-        <v>256</v>
-      </c>
-      <c r="O74" t="s">
+      <c r="G74" t="s">
+        <v>256</v>
+      </c>
+      <c r="M74" t="s">
         <v>256</v>
       </c>
       <c r="P74" t="s">
         <v>256</v>
       </c>
-      <c r="S74" t="s">
+      <c r="Q74" t="s">
         <v>256</v>
       </c>
       <c r="T74" t="s">
@@ -9397,7 +9517,7 @@
       <c r="U74" t="s">
         <v>256</v>
       </c>
-      <c r="W74" t="s">
+      <c r="V74" t="s">
         <v>256</v>
       </c>
       <c r="X74" t="s">
@@ -9409,67 +9529,67 @@
       <c r="Z74" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="75" spans="1:26">
+      <c r="AA74" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="75" spans="1:27">
       <c r="A75" t="s">
         <v>86</v>
       </c>
       <c r="B75" t="s">
         <v>256</v>
       </c>
-      <c r="F75" t="s">
-        <v>256</v>
-      </c>
-      <c r="P75" t="s">
+      <c r="G75" t="s">
         <v>256</v>
       </c>
       <c r="Q75" t="s">
         <v>256</v>
       </c>
-      <c r="T75" t="s">
+      <c r="R75" t="s">
         <v>256</v>
       </c>
       <c r="U75" t="s">
         <v>256</v>
       </c>
-      <c r="W75" t="s">
+      <c r="V75" t="s">
         <v>256</v>
       </c>
       <c r="X75" t="s">
         <v>256</v>
       </c>
-      <c r="Z75" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="76" spans="1:26">
+      <c r="Y75" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA75" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="76" spans="1:27">
       <c r="A76" t="s">
         <v>87</v>
       </c>
-      <c r="P76" t="s">
-        <v>256</v>
-      </c>
-      <c r="S76" t="s">
-        <v>256</v>
-      </c>
-      <c r="W76" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="77" spans="1:26">
+      <c r="Q76" t="s">
+        <v>256</v>
+      </c>
+      <c r="T76" t="s">
+        <v>256</v>
+      </c>
+      <c r="X76" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="77" spans="1:27">
       <c r="A77" t="s">
         <v>88</v>
       </c>
-      <c r="E77" t="s">
-        <v>256</v>
-      </c>
       <c r="F77" t="s">
         <v>256</v>
       </c>
-      <c r="L77" t="s">
-        <v>256</v>
-      </c>
-      <c r="P77" t="s">
+      <c r="G77" t="s">
+        <v>256</v>
+      </c>
+      <c r="M77" t="s">
         <v>256</v>
       </c>
       <c r="Q77" t="s">
@@ -9502,21 +9622,21 @@
       <c r="Z77" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="78" spans="1:26">
+      <c r="AA77" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="78" spans="1:27">
       <c r="A78" t="s">
         <v>89</v>
       </c>
-      <c r="E78" t="s">
-        <v>256</v>
-      </c>
       <c r="F78" t="s">
         <v>256</v>
       </c>
-      <c r="L78" t="s">
-        <v>256</v>
-      </c>
-      <c r="P78" t="s">
+      <c r="G78" t="s">
+        <v>256</v>
+      </c>
+      <c r="M78" t="s">
         <v>256</v>
       </c>
       <c r="Q78" t="s">
@@ -9534,7 +9654,7 @@
       <c r="U78" t="s">
         <v>256</v>
       </c>
-      <c r="W78" t="s">
+      <c r="V78" t="s">
         <v>256</v>
       </c>
       <c r="X78" t="s">
@@ -9546,24 +9666,24 @@
       <c r="Z78" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="79" spans="1:26">
+      <c r="AA78" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="79" spans="1:27">
       <c r="A79" t="s">
         <v>90</v>
       </c>
-      <c r="E79" t="s">
-        <v>256</v>
-      </c>
       <c r="F79" t="s">
         <v>256</v>
       </c>
-      <c r="L79" t="s">
-        <v>256</v>
-      </c>
-      <c r="P79" t="s">
-        <v>256</v>
-      </c>
-      <c r="R79" t="s">
+      <c r="G79" t="s">
+        <v>256</v>
+      </c>
+      <c r="M79" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q79" t="s">
         <v>256</v>
       </c>
       <c r="S79" t="s">
@@ -9575,7 +9695,7 @@
       <c r="U79" t="s">
         <v>256</v>
       </c>
-      <c r="W79" t="s">
+      <c r="V79" t="s">
         <v>256</v>
       </c>
       <c r="X79" t="s">
@@ -9587,21 +9707,21 @@
       <c r="Z79" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="80" spans="1:26">
+      <c r="AA79" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="80" spans="1:27">
       <c r="A80" t="s">
         <v>91</v>
       </c>
       <c r="C80" t="s">
         <v>256</v>
       </c>
-      <c r="E80" t="s">
-        <v>256</v>
-      </c>
       <c r="F80" t="s">
         <v>256</v>
       </c>
-      <c r="P80" t="s">
+      <c r="G80" t="s">
         <v>256</v>
       </c>
       <c r="Q80" t="s">
@@ -9619,7 +9739,7 @@
       <c r="U80" t="s">
         <v>256</v>
       </c>
-      <c r="W80" t="s">
+      <c r="V80" t="s">
         <v>256</v>
       </c>
       <c r="X80" t="s">
@@ -9631,24 +9751,24 @@
       <c r="Z80" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="81" spans="1:26">
+      <c r="AA80" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="81" spans="1:27">
       <c r="A81" t="s">
         <v>92</v>
       </c>
       <c r="C81" t="s">
         <v>256</v>
       </c>
-      <c r="E81" t="s">
-        <v>256</v>
-      </c>
       <c r="F81" t="s">
         <v>256</v>
       </c>
-      <c r="L81" t="s">
-        <v>256</v>
-      </c>
-      <c r="P81" t="s">
+      <c r="G81" t="s">
+        <v>256</v>
+      </c>
+      <c r="M81" t="s">
         <v>256</v>
       </c>
       <c r="Q81" t="s">
@@ -9681,24 +9801,27 @@
       <c r="Z81" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="82" spans="1:26">
+      <c r="AA81" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="82" spans="1:27">
       <c r="A82" t="s">
         <v>93</v>
       </c>
       <c r="C82" t="s">
         <v>256</v>
       </c>
-      <c r="E82" t="s">
+      <c r="D82" t="s">
         <v>256</v>
       </c>
       <c r="F82" t="s">
         <v>256</v>
       </c>
-      <c r="L82" t="s">
-        <v>256</v>
-      </c>
-      <c r="N82" t="s">
+      <c r="G82" t="s">
+        <v>256</v>
+      </c>
+      <c r="M82" t="s">
         <v>256</v>
       </c>
       <c r="O82" t="s">
@@ -9722,7 +9845,7 @@
       <c r="U82" t="s">
         <v>256</v>
       </c>
-      <c r="W82" t="s">
+      <c r="V82" t="s">
         <v>256</v>
       </c>
       <c r="X82" t="s">
@@ -9734,27 +9857,27 @@
       <c r="Z82" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="83" spans="1:26">
+      <c r="AA82" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="83" spans="1:27">
       <c r="A83" t="s">
         <v>94</v>
       </c>
       <c r="C83" t="s">
         <v>256</v>
       </c>
-      <c r="F83" t="s">
-        <v>256</v>
-      </c>
-      <c r="L83" t="s">
-        <v>256</v>
-      </c>
-      <c r="P83" t="s">
+      <c r="G83" t="s">
+        <v>256</v>
+      </c>
+      <c r="M83" t="s">
         <v>256</v>
       </c>
       <c r="Q83" t="s">
         <v>256</v>
       </c>
-      <c r="S83" t="s">
+      <c r="R83" t="s">
         <v>256</v>
       </c>
       <c r="T83" t="s">
@@ -9763,7 +9886,7 @@
       <c r="U83" t="s">
         <v>256</v>
       </c>
-      <c r="W83" t="s">
+      <c r="V83" t="s">
         <v>256</v>
       </c>
       <c r="X83" t="s">
@@ -9775,24 +9898,24 @@
       <c r="Z83" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="84" spans="1:26">
+      <c r="AA83" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="84" spans="1:27">
       <c r="A84" t="s">
         <v>95</v>
       </c>
       <c r="C84" t="s">
         <v>256</v>
       </c>
-      <c r="E84" t="s">
-        <v>256</v>
-      </c>
       <c r="F84" t="s">
         <v>256</v>
       </c>
-      <c r="L84" t="s">
-        <v>256</v>
-      </c>
-      <c r="P84" t="s">
+      <c r="G84" t="s">
+        <v>256</v>
+      </c>
+      <c r="M84" t="s">
         <v>256</v>
       </c>
       <c r="Q84" t="s">
@@ -9810,7 +9933,7 @@
       <c r="U84" t="s">
         <v>256</v>
       </c>
-      <c r="W84" t="s">
+      <c r="V84" t="s">
         <v>256</v>
       </c>
       <c r="X84" t="s">
@@ -9822,24 +9945,24 @@
       <c r="Z84" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="85" spans="1:26">
+      <c r="AA84" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="85" spans="1:27">
       <c r="A85" t="s">
         <v>96</v>
       </c>
-      <c r="E85" t="s">
-        <v>256</v>
-      </c>
       <c r="F85" t="s">
         <v>256</v>
       </c>
-      <c r="P85" t="s">
+      <c r="G85" t="s">
         <v>256</v>
       </c>
       <c r="Q85" t="s">
         <v>256</v>
       </c>
-      <c r="S85" t="s">
+      <c r="R85" t="s">
         <v>256</v>
       </c>
       <c r="T85" t="s">
@@ -9848,7 +9971,7 @@
       <c r="U85" t="s">
         <v>256</v>
       </c>
-      <c r="W85" t="s">
+      <c r="V85" t="s">
         <v>256</v>
       </c>
       <c r="X85" t="s">
@@ -9860,24 +9983,27 @@
       <c r="Z85" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="86" spans="1:26">
+      <c r="AA85" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="86" spans="1:27">
       <c r="A86" t="s">
         <v>97</v>
       </c>
       <c r="C86" t="s">
         <v>256</v>
       </c>
-      <c r="E86" t="s">
+      <c r="D86" t="s">
         <v>256</v>
       </c>
       <c r="F86" t="s">
         <v>256</v>
       </c>
-      <c r="L86" t="s">
-        <v>256</v>
-      </c>
-      <c r="O86" t="s">
+      <c r="G86" t="s">
+        <v>256</v>
+      </c>
+      <c r="M86" t="s">
         <v>256</v>
       </c>
       <c r="P86" t="s">
@@ -9898,7 +10024,7 @@
       <c r="U86" t="s">
         <v>256</v>
       </c>
-      <c r="W86" t="s">
+      <c r="V86" t="s">
         <v>256</v>
       </c>
       <c r="X86" t="s">
@@ -9910,24 +10036,24 @@
       <c r="Z86" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="87" spans="1:26">
+      <c r="AA86" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="87" spans="1:27">
       <c r="A87" t="s">
         <v>98</v>
       </c>
       <c r="C87" t="s">
         <v>256</v>
       </c>
-      <c r="E87" t="s">
-        <v>256</v>
-      </c>
       <c r="F87" t="s">
         <v>256</v>
       </c>
-      <c r="P87" t="s">
-        <v>256</v>
-      </c>
-      <c r="S87" t="s">
+      <c r="G87" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q87" t="s">
         <v>256</v>
       </c>
       <c r="T87" t="s">
@@ -9936,7 +10062,7 @@
       <c r="U87" t="s">
         <v>256</v>
       </c>
-      <c r="W87" t="s">
+      <c r="V87" t="s">
         <v>256</v>
       </c>
       <c r="X87" t="s">
@@ -9948,24 +10074,24 @@
       <c r="Z87" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="88" spans="1:26">
+      <c r="AA87" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="88" spans="1:27">
       <c r="A88" t="s">
         <v>99</v>
       </c>
-      <c r="E88" t="s">
-        <v>256</v>
-      </c>
       <c r="F88" t="s">
         <v>256</v>
       </c>
-      <c r="L88" t="s">
-        <v>256</v>
-      </c>
-      <c r="P88" t="s">
-        <v>256</v>
-      </c>
-      <c r="S88" t="s">
+      <c r="G88" t="s">
+        <v>256</v>
+      </c>
+      <c r="M88" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q88" t="s">
         <v>256</v>
       </c>
       <c r="T88" t="s">
@@ -9974,17 +10100,20 @@
       <c r="U88" t="s">
         <v>256</v>
       </c>
-      <c r="W88" t="s">
+      <c r="V88" t="s">
         <v>256</v>
       </c>
       <c r="X88" t="s">
         <v>256</v>
       </c>
-      <c r="Z88" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="89" spans="1:26">
+      <c r="Y88" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA88" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="89" spans="1:27">
       <c r="A89" t="s">
         <v>100</v>
       </c>
@@ -9997,19 +10126,19 @@
       <c r="F89" t="s">
         <v>256</v>
       </c>
-      <c r="H89" t="s">
-        <v>256</v>
-      </c>
-      <c r="L89" t="s">
-        <v>256</v>
-      </c>
-      <c r="O89" t="s">
+      <c r="G89" t="s">
+        <v>256</v>
+      </c>
+      <c r="I89" t="s">
+        <v>256</v>
+      </c>
+      <c r="M89" t="s">
         <v>256</v>
       </c>
       <c r="P89" t="s">
         <v>256</v>
       </c>
-      <c r="R89" t="s">
+      <c r="Q89" t="s">
         <v>256</v>
       </c>
       <c r="S89" t="s">
@@ -10021,7 +10150,7 @@
       <c r="U89" t="s">
         <v>256</v>
       </c>
-      <c r="W89" t="s">
+      <c r="V89" t="s">
         <v>256</v>
       </c>
       <c r="X89" t="s">
@@ -10033,8 +10162,11 @@
       <c r="Z89" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="90" spans="1:26">
+      <c r="AA89" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="90" spans="1:27">
       <c r="A90" t="s">
         <v>101</v>
       </c>
@@ -10044,16 +10176,13 @@
       <c r="C90" t="s">
         <v>256</v>
       </c>
-      <c r="E90" t="s">
-        <v>256</v>
-      </c>
       <c r="F90" t="s">
         <v>256</v>
       </c>
-      <c r="L90" t="s">
-        <v>256</v>
-      </c>
-      <c r="P90" t="s">
+      <c r="G90" t="s">
+        <v>256</v>
+      </c>
+      <c r="M90" t="s">
         <v>256</v>
       </c>
       <c r="Q90" t="s">
@@ -10071,7 +10200,7 @@
       <c r="U90" t="s">
         <v>256</v>
       </c>
-      <c r="W90" t="s">
+      <c r="V90" t="s">
         <v>256</v>
       </c>
       <c r="X90" t="s">
@@ -10083,21 +10212,21 @@
       <c r="Z90" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="91" spans="1:26">
+      <c r="AA90" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="91" spans="1:27">
       <c r="A91" t="s">
         <v>102</v>
       </c>
-      <c r="D91" t="s">
-        <v>256</v>
-      </c>
       <c r="E91" t="s">
         <v>256</v>
       </c>
-      <c r="H91" t="s">
-        <v>256</v>
-      </c>
-      <c r="P91" t="s">
+      <c r="F91" t="s">
+        <v>256</v>
+      </c>
+      <c r="I91" t="s">
         <v>256</v>
       </c>
       <c r="Q91" t="s">
@@ -10115,7 +10244,7 @@
       <c r="U91" t="s">
         <v>256</v>
       </c>
-      <c r="W91" t="s">
+      <c r="V91" t="s">
         <v>256</v>
       </c>
       <c r="X91" t="s">
@@ -10127,8 +10256,11 @@
       <c r="Z91" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="92" spans="1:26">
+      <c r="AA91" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="92" spans="1:27">
       <c r="A92" t="s">
         <v>103</v>
       </c>
@@ -10138,13 +10270,13 @@
       <c r="C92" t="s">
         <v>256</v>
       </c>
-      <c r="F92" t="s">
-        <v>256</v>
-      </c>
-      <c r="L92" t="s">
-        <v>256</v>
-      </c>
-      <c r="N92" t="s">
+      <c r="D92" t="s">
+        <v>256</v>
+      </c>
+      <c r="G92" t="s">
+        <v>256</v>
+      </c>
+      <c r="M92" t="s">
         <v>256</v>
       </c>
       <c r="O92" t="s">
@@ -10168,7 +10300,7 @@
       <c r="U92" t="s">
         <v>256</v>
       </c>
-      <c r="W92" t="s">
+      <c r="V92" t="s">
         <v>256</v>
       </c>
       <c r="X92" t="s">
@@ -10180,8 +10312,11 @@
       <c r="Z92" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="93" spans="1:26">
+      <c r="AA92" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="93" spans="1:27">
       <c r="A93" t="s">
         <v>104</v>
       </c>
@@ -10191,16 +10326,13 @@
       <c r="C93" t="s">
         <v>256</v>
       </c>
-      <c r="F93" t="s">
-        <v>256</v>
-      </c>
-      <c r="L93" t="s">
-        <v>256</v>
-      </c>
-      <c r="P93" t="s">
-        <v>256</v>
-      </c>
-      <c r="R93" t="s">
+      <c r="G93" t="s">
+        <v>256</v>
+      </c>
+      <c r="M93" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q93" t="s">
         <v>256</v>
       </c>
       <c r="S93" t="s">
@@ -10212,7 +10344,7 @@
       <c r="U93" t="s">
         <v>256</v>
       </c>
-      <c r="W93" t="s">
+      <c r="V93" t="s">
         <v>256</v>
       </c>
       <c r="X93" t="s">
@@ -10224,24 +10356,27 @@
       <c r="Z93" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="94" spans="1:26">
+      <c r="AA93" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="94" spans="1:27">
       <c r="A94" t="s">
         <v>105</v>
       </c>
       <c r="C94" t="s">
         <v>256</v>
       </c>
-      <c r="E94" t="s">
+      <c r="D94" t="s">
         <v>256</v>
       </c>
       <c r="F94" t="s">
         <v>256</v>
       </c>
-      <c r="L94" t="s">
-        <v>256</v>
-      </c>
-      <c r="O94" t="s">
+      <c r="G94" t="s">
+        <v>256</v>
+      </c>
+      <c r="M94" t="s">
         <v>256</v>
       </c>
       <c r="P94" t="s">
@@ -10262,7 +10397,7 @@
       <c r="U94" t="s">
         <v>256</v>
       </c>
-      <c r="W94" t="s">
+      <c r="V94" t="s">
         <v>256</v>
       </c>
       <c r="X94" t="s">
@@ -10274,24 +10409,24 @@
       <c r="Z94" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="95" spans="1:26">
+      <c r="AA94" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="95" spans="1:27">
       <c r="A95" t="s">
         <v>106</v>
       </c>
-      <c r="E95" t="s">
-        <v>256</v>
-      </c>
       <c r="F95" t="s">
         <v>256</v>
       </c>
-      <c r="L95" t="s">
-        <v>256</v>
-      </c>
-      <c r="P95" t="s">
-        <v>256</v>
-      </c>
-      <c r="S95" t="s">
+      <c r="G95" t="s">
+        <v>256</v>
+      </c>
+      <c r="M95" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q95" t="s">
         <v>256</v>
       </c>
       <c r="T95" t="s">
@@ -10300,36 +10435,36 @@
       <c r="U95" t="s">
         <v>256</v>
       </c>
-      <c r="W95" t="s">
+      <c r="V95" t="s">
         <v>256</v>
       </c>
       <c r="X95" t="s">
         <v>256</v>
       </c>
-      <c r="Z95" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="96" spans="1:26">
+      <c r="Y95" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA95" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="96" spans="1:27">
       <c r="A96" t="s">
         <v>107</v>
       </c>
-      <c r="F96" t="s">
-        <v>256</v>
-      </c>
-      <c r="I96" t="s">
+      <c r="G96" t="s">
         <v>256</v>
       </c>
       <c r="J96" t="s">
         <v>256</v>
       </c>
-      <c r="N96" t="s">
-        <v>256</v>
-      </c>
-      <c r="P96" t="s">
-        <v>256</v>
-      </c>
-      <c r="R96" t="s">
+      <c r="K96" t="s">
+        <v>256</v>
+      </c>
+      <c r="O96" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q96" t="s">
         <v>256</v>
       </c>
       <c r="S96" t="s">
@@ -10341,7 +10476,7 @@
       <c r="U96" t="s">
         <v>256</v>
       </c>
-      <c r="W96" t="s">
+      <c r="V96" t="s">
         <v>256</v>
       </c>
       <c r="X96" t="s">
@@ -10353,56 +10488,59 @@
       <c r="Z96" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="97" spans="1:26">
+      <c r="AA96" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="97" spans="1:27">
       <c r="A97" t="s">
         <v>108</v>
       </c>
-      <c r="D97" t="s">
-        <v>256</v>
-      </c>
-      <c r="H97" t="s">
-        <v>256</v>
-      </c>
-      <c r="L97" t="s">
-        <v>256</v>
-      </c>
-      <c r="P97" t="s">
-        <v>256</v>
-      </c>
-      <c r="S97" t="s">
-        <v>256</v>
-      </c>
-      <c r="U97" t="s">
-        <v>256</v>
-      </c>
-      <c r="W97" t="s">
+      <c r="E97" t="s">
+        <v>256</v>
+      </c>
+      <c r="I97" t="s">
+        <v>256</v>
+      </c>
+      <c r="M97" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>256</v>
+      </c>
+      <c r="T97" t="s">
+        <v>256</v>
+      </c>
+      <c r="V97" t="s">
         <v>256</v>
       </c>
       <c r="X97" t="s">
         <v>256</v>
       </c>
-      <c r="Z97" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="98" spans="1:26">
+      <c r="Y97" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA97" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="98" spans="1:27">
       <c r="A98" t="s">
         <v>109</v>
       </c>
       <c r="C98" t="s">
         <v>256</v>
       </c>
-      <c r="E98" t="s">
+      <c r="D98" t="s">
         <v>256</v>
       </c>
       <c r="F98" t="s">
         <v>256</v>
       </c>
-      <c r="L98" t="s">
-        <v>256</v>
-      </c>
-      <c r="O98" t="s">
+      <c r="G98" t="s">
+        <v>256</v>
+      </c>
+      <c r="M98" t="s">
         <v>256</v>
       </c>
       <c r="P98" t="s">
@@ -10423,7 +10561,7 @@
       <c r="U98" t="s">
         <v>256</v>
       </c>
-      <c r="W98" t="s">
+      <c r="V98" t="s">
         <v>256</v>
       </c>
       <c r="X98" t="s">
@@ -10435,33 +10573,36 @@
       <c r="Z98" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="99" spans="1:26">
+      <c r="AA98" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="99" spans="1:27">
       <c r="A99" t="s">
         <v>110</v>
       </c>
       <c r="C99" t="s">
         <v>256</v>
       </c>
-      <c r="F99" t="s">
-        <v>256</v>
-      </c>
-      <c r="L99" t="s">
-        <v>256</v>
-      </c>
-      <c r="O99" t="s">
+      <c r="D99" t="s">
+        <v>256</v>
+      </c>
+      <c r="G99" t="s">
+        <v>256</v>
+      </c>
+      <c r="M99" t="s">
         <v>256</v>
       </c>
       <c r="P99" t="s">
         <v>256</v>
       </c>
-      <c r="S99" t="s">
-        <v>256</v>
-      </c>
-      <c r="U99" t="s">
-        <v>256</v>
-      </c>
-      <c r="W99" t="s">
+      <c r="Q99" t="s">
+        <v>256</v>
+      </c>
+      <c r="T99" t="s">
+        <v>256</v>
+      </c>
+      <c r="V99" t="s">
         <v>256</v>
       </c>
       <c r="X99" t="s">
@@ -10473,24 +10614,24 @@
       <c r="Z99" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="100" spans="1:26">
+      <c r="AA99" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="100" spans="1:27">
       <c r="A100" t="s">
         <v>111</v>
       </c>
       <c r="C100" t="s">
         <v>256</v>
       </c>
-      <c r="E100" t="s">
-        <v>256</v>
-      </c>
       <c r="F100" t="s">
         <v>256</v>
       </c>
-      <c r="L100" t="s">
-        <v>256</v>
-      </c>
-      <c r="P100" t="s">
+      <c r="G100" t="s">
+        <v>256</v>
+      </c>
+      <c r="M100" t="s">
         <v>256</v>
       </c>
       <c r="Q100" t="s">
@@ -10508,7 +10649,7 @@
       <c r="U100" t="s">
         <v>256</v>
       </c>
-      <c r="W100" t="s">
+      <c r="V100" t="s">
         <v>256</v>
       </c>
       <c r="X100" t="s">
@@ -10520,24 +10661,27 @@
       <c r="Z100" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="101" spans="1:26">
+      <c r="AA100" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="101" spans="1:27">
       <c r="A101" t="s">
         <v>112</v>
       </c>
       <c r="C101" t="s">
         <v>256</v>
       </c>
-      <c r="E101" t="s">
+      <c r="D101" t="s">
         <v>256</v>
       </c>
       <c r="F101" t="s">
         <v>256</v>
       </c>
-      <c r="L101" t="s">
-        <v>256</v>
-      </c>
-      <c r="N101" t="s">
+      <c r="G101" t="s">
+        <v>256</v>
+      </c>
+      <c r="M101" t="s">
         <v>256</v>
       </c>
       <c r="O101" t="s">
@@ -10549,7 +10693,7 @@
       <c r="Q101" t="s">
         <v>256</v>
       </c>
-      <c r="S101" t="s">
+      <c r="R101" t="s">
         <v>256</v>
       </c>
       <c r="T101" t="s">
@@ -10558,7 +10702,7 @@
       <c r="U101" t="s">
         <v>256</v>
       </c>
-      <c r="W101" t="s">
+      <c r="V101" t="s">
         <v>256</v>
       </c>
       <c r="X101" t="s">
@@ -10570,21 +10714,24 @@
       <c r="Z101" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="102" spans="1:26">
+      <c r="AA101" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="102" spans="1:27">
       <c r="A102" t="s">
         <v>113</v>
       </c>
-      <c r="E102" t="s">
+      <c r="D102" t="s">
         <v>256</v>
       </c>
       <c r="F102" t="s">
         <v>256</v>
       </c>
-      <c r="L102" t="s">
-        <v>256</v>
-      </c>
-      <c r="O102" t="s">
+      <c r="G102" t="s">
+        <v>256</v>
+      </c>
+      <c r="M102" t="s">
         <v>256</v>
       </c>
       <c r="P102" t="s">
@@ -10605,7 +10752,7 @@
       <c r="U102" t="s">
         <v>256</v>
       </c>
-      <c r="W102" t="s">
+      <c r="V102" t="s">
         <v>256</v>
       </c>
       <c r="X102" t="s">
@@ -10617,8 +10764,11 @@
       <c r="Z102" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="103" spans="1:26">
+      <c r="AA102" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="103" spans="1:27">
       <c r="A103" t="s">
         <v>114</v>
       </c>
@@ -10631,13 +10781,13 @@
       <c r="F103" t="s">
         <v>256</v>
       </c>
-      <c r="H103" t="s">
-        <v>256</v>
-      </c>
-      <c r="L103" t="s">
-        <v>256</v>
-      </c>
-      <c r="O103" t="s">
+      <c r="G103" t="s">
+        <v>256</v>
+      </c>
+      <c r="I103" t="s">
+        <v>256</v>
+      </c>
+      <c r="M103" t="s">
         <v>256</v>
       </c>
       <c r="P103" t="s">
@@ -10658,7 +10808,7 @@
       <c r="U103" t="s">
         <v>256</v>
       </c>
-      <c r="W103" t="s">
+      <c r="V103" t="s">
         <v>256</v>
       </c>
       <c r="X103" t="s">
@@ -10670,24 +10820,24 @@
       <c r="Z103" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="104" spans="1:26">
+      <c r="AA103" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="104" spans="1:27">
       <c r="A104" t="s">
         <v>115</v>
       </c>
       <c r="C104" t="s">
         <v>256</v>
       </c>
-      <c r="D104" t="s">
-        <v>256</v>
-      </c>
-      <c r="P104" t="s">
+      <c r="E104" t="s">
         <v>256</v>
       </c>
       <c r="Q104" t="s">
         <v>256</v>
       </c>
-      <c r="S104" t="s">
+      <c r="R104" t="s">
         <v>256</v>
       </c>
       <c r="T104" t="s">
@@ -10696,33 +10846,33 @@
       <c r="U104" t="s">
         <v>256</v>
       </c>
-      <c r="W104" t="s">
+      <c r="V104" t="s">
         <v>256</v>
       </c>
       <c r="X104" t="s">
         <v>256</v>
       </c>
-      <c r="Z104" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="105" spans="1:26">
+      <c r="Y104" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA104" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="105" spans="1:27">
       <c r="A105" t="s">
         <v>116</v>
       </c>
-      <c r="E105" t="s">
-        <v>256</v>
-      </c>
       <c r="F105" t="s">
         <v>256</v>
       </c>
-      <c r="L105" t="s">
-        <v>256</v>
-      </c>
-      <c r="P105" t="s">
-        <v>256</v>
-      </c>
-      <c r="R105" t="s">
+      <c r="G105" t="s">
+        <v>256</v>
+      </c>
+      <c r="M105" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q105" t="s">
         <v>256</v>
       </c>
       <c r="S105" t="s">
@@ -10734,65 +10884,68 @@
       <c r="U105" t="s">
         <v>256</v>
       </c>
-      <c r="W105" t="s">
+      <c r="V105" t="s">
         <v>256</v>
       </c>
       <c r="X105" t="s">
         <v>256</v>
       </c>
-      <c r="Z105" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="106" spans="1:26">
+      <c r="Y105" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA105" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="106" spans="1:27">
       <c r="A106" t="s">
         <v>117</v>
       </c>
       <c r="C106" t="s">
         <v>256</v>
       </c>
-      <c r="F106" t="s">
-        <v>256</v>
-      </c>
-      <c r="L106" t="s">
-        <v>256</v>
-      </c>
-      <c r="P106" t="s">
-        <v>256</v>
-      </c>
-      <c r="U106" t="s">
-        <v>256</v>
-      </c>
-      <c r="W106" t="s">
+      <c r="G106" t="s">
+        <v>256</v>
+      </c>
+      <c r="M106" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>256</v>
+      </c>
+      <c r="V106" t="s">
         <v>256</v>
       </c>
       <c r="X106" t="s">
         <v>256</v>
       </c>
-      <c r="Z106" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="107" spans="1:26">
+      <c r="Y106" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA106" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="107" spans="1:27">
       <c r="A107" t="s">
         <v>118</v>
       </c>
-      <c r="E107" t="s">
+      <c r="D107" t="s">
         <v>256</v>
       </c>
       <c r="F107" t="s">
         <v>256</v>
       </c>
-      <c r="L107" t="s">
-        <v>256</v>
-      </c>
-      <c r="O107" t="s">
+      <c r="G107" t="s">
+        <v>256</v>
+      </c>
+      <c r="M107" t="s">
         <v>256</v>
       </c>
       <c r="P107" t="s">
         <v>256</v>
       </c>
-      <c r="R107" t="s">
+      <c r="Q107" t="s">
         <v>256</v>
       </c>
       <c r="S107" t="s">
@@ -10804,7 +10957,7 @@
       <c r="U107" t="s">
         <v>256</v>
       </c>
-      <c r="W107" t="s">
+      <c r="V107" t="s">
         <v>256</v>
       </c>
       <c r="X107" t="s">
@@ -10816,24 +10969,24 @@
       <c r="Z107" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="108" spans="1:26">
+      <c r="AA107" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="108" spans="1:27">
       <c r="A108" t="s">
         <v>119</v>
       </c>
       <c r="C108" t="s">
         <v>256</v>
       </c>
-      <c r="E108" t="s">
-        <v>256</v>
-      </c>
       <c r="F108" t="s">
         <v>256</v>
       </c>
-      <c r="L108" t="s">
-        <v>256</v>
-      </c>
-      <c r="P108" t="s">
+      <c r="G108" t="s">
+        <v>256</v>
+      </c>
+      <c r="M108" t="s">
         <v>256</v>
       </c>
       <c r="Q108" t="s">
@@ -10866,24 +11019,27 @@
       <c r="Z108" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="109" spans="1:26">
+      <c r="AA108" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="109" spans="1:27">
       <c r="A109" t="s">
         <v>120</v>
       </c>
       <c r="C109" t="s">
         <v>256</v>
       </c>
-      <c r="E109" t="s">
+      <c r="D109" t="s">
         <v>256</v>
       </c>
       <c r="F109" t="s">
         <v>256</v>
       </c>
-      <c r="L109" t="s">
-        <v>256</v>
-      </c>
-      <c r="O109" t="s">
+      <c r="G109" t="s">
+        <v>256</v>
+      </c>
+      <c r="M109" t="s">
         <v>256</v>
       </c>
       <c r="P109" t="s">
@@ -10904,7 +11060,7 @@
       <c r="U109" t="s">
         <v>256</v>
       </c>
-      <c r="W109" t="s">
+      <c r="V109" t="s">
         <v>256</v>
       </c>
       <c r="X109" t="s">
@@ -10916,21 +11072,21 @@
       <c r="Z109" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="110" spans="1:26">
+      <c r="AA109" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="110" spans="1:27">
       <c r="A110" t="s">
         <v>121</v>
       </c>
       <c r="B110" t="s">
         <v>256</v>
       </c>
-      <c r="F110" t="s">
-        <v>256</v>
-      </c>
-      <c r="L110" t="s">
-        <v>256</v>
-      </c>
-      <c r="P110" t="s">
+      <c r="G110" t="s">
+        <v>256</v>
+      </c>
+      <c r="M110" t="s">
         <v>256</v>
       </c>
       <c r="Q110" t="s">
@@ -10948,7 +11104,7 @@
       <c r="U110" t="s">
         <v>256</v>
       </c>
-      <c r="X110" t="s">
+      <c r="V110" t="s">
         <v>256</v>
       </c>
       <c r="Y110" t="s">
@@ -10957,24 +11113,27 @@
       <c r="Z110" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="111" spans="1:26">
+      <c r="AA110" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="111" spans="1:27">
       <c r="A111" t="s">
         <v>122</v>
       </c>
       <c r="C111" t="s">
         <v>256</v>
       </c>
-      <c r="E111" t="s">
+      <c r="D111" t="s">
         <v>256</v>
       </c>
       <c r="F111" t="s">
         <v>256</v>
       </c>
-      <c r="L111" t="s">
-        <v>256</v>
-      </c>
-      <c r="O111" t="s">
+      <c r="G111" t="s">
+        <v>256</v>
+      </c>
+      <c r="M111" t="s">
         <v>256</v>
       </c>
       <c r="P111" t="s">
@@ -10995,7 +11154,7 @@
       <c r="U111" t="s">
         <v>256</v>
       </c>
-      <c r="W111" t="s">
+      <c r="V111" t="s">
         <v>256</v>
       </c>
       <c r="X111" t="s">
@@ -11007,24 +11166,27 @@
       <c r="Z111" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="112" spans="1:26">
+      <c r="AA111" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="112" spans="1:27">
       <c r="A112" t="s">
         <v>123</v>
       </c>
       <c r="C112" t="s">
         <v>256</v>
       </c>
-      <c r="E112" t="s">
+      <c r="D112" t="s">
         <v>256</v>
       </c>
       <c r="F112" t="s">
         <v>256</v>
       </c>
-      <c r="L112" t="s">
-        <v>256</v>
-      </c>
-      <c r="O112" t="s">
+      <c r="G112" t="s">
+        <v>256</v>
+      </c>
+      <c r="M112" t="s">
         <v>256</v>
       </c>
       <c r="P112" t="s">
@@ -11045,7 +11207,7 @@
       <c r="U112" t="s">
         <v>256</v>
       </c>
-      <c r="W112" t="s">
+      <c r="V112" t="s">
         <v>256</v>
       </c>
       <c r="X112" t="s">
@@ -11057,18 +11219,21 @@
       <c r="Z112" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="113" spans="1:26">
+      <c r="AA112" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="113" spans="1:27">
       <c r="A113" t="s">
         <v>124</v>
       </c>
       <c r="D113" t="s">
         <v>256</v>
       </c>
-      <c r="F113" t="s">
-        <v>256</v>
-      </c>
-      <c r="H113" t="s">
+      <c r="E113" t="s">
+        <v>256</v>
+      </c>
+      <c r="G113" t="s">
         <v>256</v>
       </c>
       <c r="I113" t="s">
@@ -11077,25 +11242,25 @@
       <c r="J113" t="s">
         <v>256</v>
       </c>
-      <c r="L113" t="s">
-        <v>256</v>
-      </c>
-      <c r="O113" t="s">
+      <c r="K113" t="s">
+        <v>256</v>
+      </c>
+      <c r="M113" t="s">
         <v>256</v>
       </c>
       <c r="P113" t="s">
         <v>256</v>
       </c>
-      <c r="R113" t="s">
+      <c r="Q113" t="s">
         <v>256</v>
       </c>
       <c r="S113" t="s">
         <v>256</v>
       </c>
-      <c r="U113" t="s">
-        <v>256</v>
-      </c>
-      <c r="W113" t="s">
+      <c r="T113" t="s">
+        <v>256</v>
+      </c>
+      <c r="V113" t="s">
         <v>256</v>
       </c>
       <c r="X113" t="s">
@@ -11107,30 +11272,33 @@
       <c r="Z113" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="114" spans="1:26">
+      <c r="AA113" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="114" spans="1:27">
       <c r="A114" t="s">
         <v>125</v>
       </c>
       <c r="C114" t="s">
         <v>256</v>
       </c>
-      <c r="E114" t="s">
+      <c r="D114" t="s">
         <v>256</v>
       </c>
       <c r="F114" t="s">
         <v>256</v>
       </c>
-      <c r="L114" t="s">
-        <v>256</v>
-      </c>
-      <c r="O114" t="s">
+      <c r="G114" t="s">
+        <v>256</v>
+      </c>
+      <c r="M114" t="s">
         <v>256</v>
       </c>
       <c r="P114" t="s">
         <v>256</v>
       </c>
-      <c r="R114" t="s">
+      <c r="Q114" t="s">
         <v>256</v>
       </c>
       <c r="S114" t="s">
@@ -11142,7 +11310,7 @@
       <c r="U114" t="s">
         <v>256</v>
       </c>
-      <c r="W114" t="s">
+      <c r="V114" t="s">
         <v>256</v>
       </c>
       <c r="X114" t="s">
@@ -11152,6 +11320,9 @@
         <v>256</v>
       </c>
       <c r="Z114" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA114" t="s">
         <v>256</v>
       </c>
     </row>
@@ -11170,79 +11341,79 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="R1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="S1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="T1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="V1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="W1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="X1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Y1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Z1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="2" spans="1:26">
@@ -16079,10 +16250,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="B1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2" spans="1:3">
